--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2549,6 +2549,3731 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122483519</v>
+      </c>
+      <c r="B17" t="n">
+        <v>74752</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>394595</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7061889</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122483517</v>
+      </c>
+      <c r="B18" t="n">
+        <v>74564</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>394786</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7061968</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122483514</v>
+      </c>
+      <c r="B19" t="n">
+        <v>74757</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>394834</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7062076</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122481482</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78735</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>394669</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7062253</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122481467</v>
+      </c>
+      <c r="B21" t="n">
+        <v>77588</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>394746</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7062338</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>bark på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122483523</v>
+      </c>
+      <c r="B22" t="n">
+        <v>74747</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>310</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>394544</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7061898</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122481492</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79768</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>394589</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7061895</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122481486</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79733</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>394648</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7062211</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>grankvistar # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122481496</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78814</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>394790</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7062334</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>på granar gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122483521</v>
+      </c>
+      <c r="B26" t="n">
+        <v>94707</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>394553</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7061889</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Lodyta, intermediär</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122481493</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78735</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>283</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>394812</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7062006</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122481491</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90826</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>394563</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7061882</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122483534</v>
+      </c>
+      <c r="B29" t="n">
+        <v>77587</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>394734</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7062334</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122483532</v>
+      </c>
+      <c r="B30" t="n">
+        <v>82438</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>394743</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7062322</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122481479</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78651</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>394730</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7062309</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122481474</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57532</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>394742</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7062294</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122483536</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78814</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>394745</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7062367</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122481483</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57379</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>394537</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7061922</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122481494</v>
+      </c>
+      <c r="B35" t="n">
+        <v>77588</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>394802</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7062015</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122483511</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78735</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>283</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>394793</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7062355</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122483535</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78735</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>283</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>394742</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7062337</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122483533</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78814</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>394737</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7062329</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122481473</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78735</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>283</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>394712</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7062279</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122483537</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78735</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>283</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>394745</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7062367</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122483529</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78814</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>394652</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7062221</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122481475</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78907</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>394738</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7062311</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122481495</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78651</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>394826</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7062076</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122483516</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79768</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>394830</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7062019</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122483518</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78814</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>394636</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7061901</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122481464</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78735</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>283</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>394733</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7062344</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122481477</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78814</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>394730</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7062309</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>grenar på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122481466</v>
+      </c>
+      <c r="B48" t="n">
+        <v>74752</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>394746</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7062338</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>bark på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2668,10 +2668,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122483517</v>
+        <v>122481482</v>
       </c>
       <c r="B18" t="n">
-        <v>74564</v>
+        <v>78735</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,25 +2680,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6428</v>
+        <v>283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394786</v>
+        <v>394669</v>
       </c>
       <c r="R18" t="n">
-        <v>7061968</v>
+        <v>7062253</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,28 +2767,28 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122483514</v>
+        <v>122483517</v>
       </c>
       <c r="B19" t="n">
-        <v>74757</v>
+        <v>74564</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>6428</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394834</v>
+        <v>394786</v>
       </c>
       <c r="R19" t="n">
-        <v>7062076</v>
+        <v>7061968</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122481482</v>
+        <v>122483514</v>
       </c>
       <c r="B20" t="n">
-        <v>78735</v>
+        <v>74757</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>283</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394669</v>
+        <v>394834</v>
       </c>
       <c r="R20" t="n">
-        <v>7062253</v>
+        <v>7062076</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3001,18 +3001,18 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122481492</v>
+        <v>122483521</v>
       </c>
       <c r="B23" t="n">
-        <v>79768</v>
+        <v>94707</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3270,21 +3270,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>2668</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3294,13 +3294,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394589</v>
+        <v>394553</v>
       </c>
       <c r="R23" t="n">
-        <v>7061895</v>
+        <v>7061889</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3341,40 +3341,30 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122481486</v>
+        <v>122481492</v>
       </c>
       <c r="B24" t="n">
-        <v>79733</v>
+        <v>79768</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3383,25 +3373,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3411,10 +3401,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394648</v>
+        <v>394589</v>
       </c>
       <c r="R24" t="n">
-        <v>7062211</v>
+        <v>7061895</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3460,17 +3450,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3488,10 +3478,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122481496</v>
+        <v>122481486</v>
       </c>
       <c r="B25" t="n">
-        <v>78814</v>
+        <v>79733</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3500,25 +3490,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3528,10 +3518,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394790</v>
+        <v>394648</v>
       </c>
       <c r="R25" t="n">
-        <v>7062334</v>
+        <v>7062211</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3587,7 +3577,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3605,10 +3595,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122483521</v>
+        <v>122481496</v>
       </c>
       <c r="B26" t="n">
-        <v>94707</v>
+        <v>78814</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3617,25 +3607,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2668</v>
+        <v>1249</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3645,13 +3635,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394553</v>
+        <v>394790</v>
       </c>
       <c r="R26" t="n">
-        <v>7061889</v>
+        <v>7062334</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3692,20 +3682,30 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -4408,10 +4408,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483536</v>
+        <v>122481483</v>
       </c>
       <c r="B33" t="n">
-        <v>78814</v>
+        <v>57379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4420,41 +4420,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394745</v>
+        <v>394537</v>
       </c>
       <c r="R33" t="n">
-        <v>7062367</v>
+        <v>7061922</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4486,6 +4491,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4494,41 +4504,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481483</v>
+        <v>122483536</v>
       </c>
       <c r="B34" t="n">
-        <v>57379</v>
+        <v>78814</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4537,46 +4532,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394537</v>
+        <v>394745</v>
       </c>
       <c r="R34" t="n">
-        <v>7061922</v>
+        <v>7062367</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4608,11 +4598,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4621,16 +4606,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122483511</v>
+        <v>122481473</v>
       </c>
       <c r="B36" t="n">
         <v>78735</v>
@@ -4794,13 +4794,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394793</v>
+        <v>394712</v>
       </c>
       <c r="R36" t="n">
-        <v>7062355</v>
+        <v>7062279</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4853,25 +4853,25 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483535</v>
+        <v>122483511</v>
       </c>
       <c r="B37" t="n">
         <v>78735</v>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394742</v>
+        <v>394793</v>
       </c>
       <c r="R37" t="n">
-        <v>7062337</v>
+        <v>7062355</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483533</v>
+        <v>122483535</v>
       </c>
       <c r="B38" t="n">
-        <v>78814</v>
+        <v>78735</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5000,25 +5000,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394737</v>
+        <v>394742</v>
       </c>
       <c r="R38" t="n">
-        <v>7062329</v>
+        <v>7062337</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -5105,10 +5105,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481473</v>
+        <v>122483533</v>
       </c>
       <c r="B39" t="n">
-        <v>78735</v>
+        <v>78814</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5117,25 +5117,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5145,13 +5145,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394712</v>
+        <v>394737</v>
       </c>
       <c r="R39" t="n">
-        <v>7062279</v>
+        <v>7062329</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5204,18 +5204,18 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122483519</v>
+        <v>122481486</v>
       </c>
       <c r="B17" t="n">
-        <v>74752</v>
+        <v>79734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2567,21 +2567,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,13 +2586,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394595</v>
+        <v>394648</v>
       </c>
       <c r="R17" t="n">
-        <v>7061889</v>
+        <v>7062211</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2638,11 +2633,6 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK17" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2650,28 +2640,28 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122481482</v>
+        <v>122481493</v>
       </c>
       <c r="B18" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2686,11 +2676,6 @@
       <c r="E18" t="n">
         <v>283</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Hypogymnia hultenii</t>
@@ -2708,10 +2693,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394669</v>
+        <v>394812</v>
       </c>
       <c r="R18" t="n">
-        <v>7062253</v>
+        <v>7062006</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2754,11 +2739,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
@@ -2785,10 +2765,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122483517</v>
+        <v>122481479</v>
       </c>
       <c r="B19" t="n">
-        <v>74564</v>
+        <v>78652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,25 +2777,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6428</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Rostfläck</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2825,13 +2800,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394786</v>
+        <v>394730</v>
       </c>
       <c r="R19" t="n">
-        <v>7061968</v>
+        <v>7062309</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2871,11 +2846,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
@@ -2890,22 +2860,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122483514</v>
+        <v>122481467</v>
       </c>
       <c r="B20" t="n">
-        <v>74757</v>
+        <v>77589</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2918,21 +2888,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
+        <v>228579</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2942,13 +2907,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394834</v>
+        <v>394746</v>
       </c>
       <c r="R20" t="n">
-        <v>7062076</v>
+        <v>7062338</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2989,11 +2954,6 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK20" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3001,28 +2961,28 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122481467</v>
+        <v>122483532</v>
       </c>
       <c r="B21" t="n">
-        <v>77588</v>
+        <v>82439</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3035,21 +2995,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
+        <v>1312</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3059,13 +3014,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394746</v>
+        <v>394743</v>
       </c>
       <c r="R21" t="n">
-        <v>7062338</v>
+        <v>7062322</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3106,11 +3061,6 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK21" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3118,28 +3068,28 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122483523</v>
+        <v>122483533</v>
       </c>
       <c r="B22" t="n">
-        <v>74747</v>
+        <v>78815</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3148,25 +3098,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>310</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Nordlig nållav</t>
-        </is>
+        <v>1249</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3176,10 +3121,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394544</v>
+        <v>394737</v>
       </c>
       <c r="R22" t="n">
-        <v>7061898</v>
+        <v>7062329</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3220,14 +3165,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
@@ -3254,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122483521</v>
+        <v>122483519</v>
       </c>
       <c r="B23" t="n">
-        <v>94707</v>
+        <v>74753</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3266,25 +3205,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2668</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Trubbfjädermossa</t>
-        </is>
+        <v>6440</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3294,7 +3228,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394553</v>
+        <v>394595</v>
       </c>
       <c r="R23" t="n">
         <v>7061889</v>
@@ -3341,9 +3275,14 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3361,10 +3300,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122481492</v>
+        <v>122483536</v>
       </c>
       <c r="B24" t="n">
-        <v>79768</v>
+        <v>78815</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3373,25 +3312,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
+        <v>1249</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3401,13 +3335,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394589</v>
+        <v>394745</v>
       </c>
       <c r="R24" t="n">
-        <v>7061895</v>
+        <v>7062367</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3448,40 +3382,35 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122481486</v>
+        <v>122483534</v>
       </c>
       <c r="B25" t="n">
-        <v>79733</v>
+        <v>77588</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3490,25 +3419,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6000248</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3518,13 +3442,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394648</v>
+        <v>394734</v>
       </c>
       <c r="R25" t="n">
-        <v>7062211</v>
+        <v>7062334</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3562,14 +3486,10 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK25" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3577,28 +3497,28 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481496</v>
+        <v>122483521</v>
       </c>
       <c r="B26" t="n">
-        <v>78814</v>
+        <v>94716</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3607,25 +3527,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1249</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Norsk näverlav</t>
-        </is>
+        <v>2668</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3635,13 +3550,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394790</v>
+        <v>394553</v>
       </c>
       <c r="R26" t="n">
-        <v>7062334</v>
+        <v>7061889</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3682,40 +3597,30 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122481493</v>
+        <v>122481464</v>
       </c>
       <c r="B27" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,11 +3635,6 @@
       <c r="E27" t="n">
         <v>283</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Hypogymnia hultenii</t>
@@ -3752,10 +3652,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394812</v>
+        <v>394733</v>
       </c>
       <c r="R27" t="n">
-        <v>7062006</v>
+        <v>7062344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3798,11 +3698,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
@@ -3829,10 +3724,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122481491</v>
+        <v>122483514</v>
       </c>
       <c r="B28" t="n">
-        <v>90826</v>
+        <v>74758</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3845,21 +3740,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>1467</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3869,13 +3759,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394563</v>
+        <v>394834</v>
       </c>
       <c r="R28" t="n">
-        <v>7061882</v>
+        <v>7062076</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3915,11 +3805,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
@@ -3934,22 +3819,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122483534</v>
+        <v>122483537</v>
       </c>
       <c r="B29" t="n">
-        <v>77587</v>
+        <v>78736</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3958,25 +3843,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6000248</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Mörk kådsvartspik</t>
-        </is>
+        <v>283</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3986,10 +3866,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394734</v>
+        <v>394745</v>
       </c>
       <c r="R29" t="n">
-        <v>7062334</v>
+        <v>7062367</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -4030,14 +3910,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
@@ -4064,10 +3938,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483532</v>
+        <v>122481491</v>
       </c>
       <c r="B30" t="n">
-        <v>82438</v>
+        <v>90831</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4080,21 +3954,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4104,13 +3973,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394743</v>
+        <v>394563</v>
       </c>
       <c r="R30" t="n">
-        <v>7062322</v>
+        <v>7061882</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4150,11 +4019,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
@@ -4169,22 +4033,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481479</v>
+        <v>122481483</v>
       </c>
       <c r="B31" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4197,34 +4061,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394730</v>
+        <v>394537</v>
       </c>
       <c r="R31" t="n">
-        <v>7062309</v>
+        <v>7061922</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4259,6 +4123,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4267,21 +4136,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4298,10 +4152,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481474</v>
+        <v>122481495</v>
       </c>
       <c r="B32" t="n">
-        <v>57532</v>
+        <v>78652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4314,42 +4168,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394742</v>
+        <v>394826</v>
       </c>
       <c r="R32" t="n">
-        <v>7062294</v>
+        <v>7062076</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4392,6 +4233,16 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4408,10 +4259,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122481483</v>
+        <v>122483516</v>
       </c>
       <c r="B33" t="n">
-        <v>57379</v>
+        <v>79769</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4420,46 +4271,36 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6464</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394537</v>
+        <v>394830</v>
       </c>
       <c r="R33" t="n">
-        <v>7061922</v>
+        <v>7062019</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4491,39 +4332,45 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122483536</v>
+        <v>122481482</v>
       </c>
       <c r="B34" t="n">
-        <v>78814</v>
+        <v>78736</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4532,25 +4379,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1249</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Norsk näverlav</t>
-        </is>
+        <v>283</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4560,13 +4402,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394745</v>
+        <v>394669</v>
       </c>
       <c r="R34" t="n">
-        <v>7062367</v>
+        <v>7062253</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4607,40 +4449,35 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122481494</v>
+        <v>122483535</v>
       </c>
       <c r="B35" t="n">
-        <v>77588</v>
+        <v>78736</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4653,21 +4490,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
+        <v>283</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4677,13 +4509,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394802</v>
+        <v>394742</v>
       </c>
       <c r="R35" t="n">
-        <v>7062015</v>
+        <v>7062337</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4724,11 +4556,6 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK35" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4736,28 +4563,28 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122481473</v>
+        <v>122481466</v>
       </c>
       <c r="B36" t="n">
-        <v>78735</v>
+        <v>74753</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4770,21 +4597,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>283</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
+        <v>6440</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4794,10 +4616,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394712</v>
+        <v>394746</v>
       </c>
       <c r="R36" t="n">
-        <v>7062279</v>
+        <v>7062338</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4841,11 +4663,6 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK36" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4853,7 +4670,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4874,7 +4691,7 @@
         <v>122483511</v>
       </c>
       <c r="B37" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4889,11 +4706,6 @@
       <c r="E37" t="n">
         <v>283</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Hypogymnia hultenii</t>
@@ -4957,11 +4769,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
@@ -4988,10 +4795,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483535</v>
+        <v>122481496</v>
       </c>
       <c r="B38" t="n">
-        <v>78735</v>
+        <v>78815</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5000,25 +4807,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>283</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
+        <v>1249</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5028,13 +4830,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394742</v>
+        <v>394790</v>
       </c>
       <c r="R38" t="n">
-        <v>7062337</v>
+        <v>7062334</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5075,11 +4877,6 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK38" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5087,28 +4884,28 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122483533</v>
+        <v>122483529</v>
       </c>
       <c r="B39" t="n">
-        <v>78814</v>
+        <v>78815</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5123,11 +4920,6 @@
       <c r="E39" t="n">
         <v>1249</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Norsk näverlav</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Platismatia norvegica</t>
@@ -5145,10 +4937,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394737</v>
+        <v>394652</v>
       </c>
       <c r="R39" t="n">
-        <v>7062329</v>
+        <v>7062221</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5191,11 +4983,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
@@ -5222,10 +5009,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122483537</v>
+        <v>122481477</v>
       </c>
       <c r="B40" t="n">
-        <v>78735</v>
+        <v>78815</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5234,25 +5021,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>283</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
+        <v>1249</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5262,13 +5044,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394745</v>
+        <v>394730</v>
       </c>
       <c r="R40" t="n">
-        <v>7062367</v>
+        <v>7062309</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5309,11 +5091,6 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK40" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5321,28 +5098,28 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122483529</v>
+        <v>122483523</v>
       </c>
       <c r="B41" t="n">
-        <v>78814</v>
+        <v>74748</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5351,25 +5128,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1249</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Norsk näverlav</t>
-        </is>
+        <v>310</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5379,10 +5151,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394652</v>
+        <v>394544</v>
       </c>
       <c r="R41" t="n">
-        <v>7062221</v>
+        <v>7061898</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5423,13 +5195,9 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
@@ -5456,10 +5224,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481475</v>
+        <v>122481494</v>
       </c>
       <c r="B42" t="n">
-        <v>78907</v>
+        <v>77589</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5468,25 +5236,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6459</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Barkkornlav</t>
-        </is>
+        <v>228579</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5496,10 +5259,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394738</v>
+        <v>394802</v>
       </c>
       <c r="R42" t="n">
-        <v>7062311</v>
+        <v>7062015</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5543,11 +5306,6 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK42" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5555,7 +5313,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5573,10 +5331,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481495</v>
+        <v>122483518</v>
       </c>
       <c r="B43" t="n">
-        <v>78651</v>
+        <v>78815</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5585,25 +5343,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>1249</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5613,13 +5366,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394826</v>
+        <v>394636</v>
       </c>
       <c r="R43" t="n">
-        <v>7062076</v>
+        <v>7061901</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5659,11 +5412,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
@@ -5678,22 +5426,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122483516</v>
+        <v>122481492</v>
       </c>
       <c r="B44" t="n">
-        <v>79768</v>
+        <v>79769</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5708,11 +5456,6 @@
       <c r="E44" t="n">
         <v>6464</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Nephroma resupinatum</t>
@@ -5730,13 +5473,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394830</v>
+        <v>394589</v>
       </c>
       <c r="R44" t="n">
-        <v>7062019</v>
+        <v>7061895</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5774,44 +5517,38 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122483518</v>
+        <v>122481475</v>
       </c>
       <c r="B45" t="n">
-        <v>78814</v>
+        <v>78908</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5820,25 +5557,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1249</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Norsk näverlav</t>
-        </is>
+        <v>6459</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5848,13 +5580,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394636</v>
+        <v>394738</v>
       </c>
       <c r="R45" t="n">
-        <v>7061901</v>
+        <v>7062311</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5894,11 +5626,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
@@ -5913,22 +5640,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122481464</v>
+        <v>122483517</v>
       </c>
       <c r="B46" t="n">
-        <v>78735</v>
+        <v>74565</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5937,25 +5664,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>283</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
+        <v>6428</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5965,13 +5687,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394733</v>
+        <v>394786</v>
       </c>
       <c r="R46" t="n">
-        <v>7062344</v>
+        <v>7061968</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6012,11 +5734,6 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK46" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -6024,28 +5741,28 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122481477</v>
+        <v>122481474</v>
       </c>
       <c r="B47" t="n">
-        <v>78814</v>
+        <v>57532</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6054,38 +5771,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1249</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Norsk näverlav</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394730</v>
+        <v>394742</v>
       </c>
       <c r="R47" t="n">
-        <v>7062309</v>
+        <v>7062294</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6128,21 +5848,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>grenar på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6159,10 +5864,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122481466</v>
+        <v>122481473</v>
       </c>
       <c r="B48" t="n">
-        <v>74752</v>
+        <v>78736</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6175,21 +5880,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>283</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,10 +5899,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394746</v>
+        <v>394712</v>
       </c>
       <c r="R48" t="n">
-        <v>7062338</v>
+        <v>7062279</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6246,11 +5946,6 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK48" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -6258,7 +5953,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -3724,10 +3724,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122483514</v>
+        <v>122483537</v>
       </c>
       <c r="B28" t="n">
-        <v>74758</v>
+        <v>78736</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3740,16 +3740,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1467</v>
+        <v>283</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394834</v>
+        <v>394745</v>
       </c>
       <c r="R28" t="n">
-        <v>7062076</v>
+        <v>7062367</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3831,10 +3831,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122483537</v>
+        <v>122483514</v>
       </c>
       <c r="B29" t="n">
-        <v>78736</v>
+        <v>74758</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3847,16 +3847,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>283</v>
+        <v>1467</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394745</v>
+        <v>394834</v>
       </c>
       <c r="R29" t="n">
-        <v>7062367</v>
+        <v>7062076</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -3938,10 +3938,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481491</v>
+        <v>122481483</v>
       </c>
       <c r="B30" t="n">
-        <v>90831</v>
+        <v>57379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3954,29 +3954,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394563</v>
+        <v>394537</v>
       </c>
       <c r="R30" t="n">
-        <v>7061882</v>
+        <v>7061922</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4011,6 +4016,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4019,16 +4029,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4045,10 +4045,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481483</v>
+        <v>122481491</v>
       </c>
       <c r="B31" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4061,34 +4061,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394537</v>
+        <v>394563</v>
       </c>
       <c r="R31" t="n">
-        <v>7061922</v>
+        <v>7061882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4123,11 +4118,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4136,6 +4126,16 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2554,7 +2554,7 @@
         <v>122481486</v>
       </c>
       <c r="B17" t="n">
-        <v>79734</v>
+        <v>79738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2569,6 +2569,11 @@
       <c r="E17" t="n">
         <v>2081</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Lobaria scrobiculata</t>
@@ -2632,6 +2637,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
@@ -2658,10 +2668,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122481493</v>
+        <v>122483516</v>
       </c>
       <c r="B18" t="n">
-        <v>78736</v>
+        <v>79773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2670,20 +2680,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>6464</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2693,13 +2708,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394812</v>
+        <v>394830</v>
       </c>
       <c r="R18" t="n">
-        <v>7062006</v>
+        <v>7062019</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2737,38 +2752,44 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122481479</v>
+        <v>122481494</v>
       </c>
       <c r="B19" t="n">
-        <v>78652</v>
+        <v>77593</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2781,16 +2802,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228579</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2800,10 +2826,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394730</v>
+        <v>394802</v>
       </c>
       <c r="R19" t="n">
-        <v>7062309</v>
+        <v>7062015</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2847,6 +2873,11 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK19" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2854,7 +2885,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2872,10 +2903,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122481467</v>
+        <v>122483523</v>
       </c>
       <c r="B20" t="n">
-        <v>77589</v>
+        <v>74752</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2888,16 +2919,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>310</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2907,13 +2943,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394746</v>
+        <v>394544</v>
       </c>
       <c r="R20" t="n">
-        <v>7062338</v>
+        <v>7061898</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2951,9 +2987,15 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK20" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2961,18 +3003,18 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2982,7 +3024,7 @@
         <v>122483532</v>
       </c>
       <c r="B21" t="n">
-        <v>82439</v>
+        <v>82443</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2997,6 +3039,11 @@
       <c r="E21" t="n">
         <v>1312</v>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Pseudographis pinicola</t>
@@ -3061,6 +3108,11 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK21" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3079,17 +3131,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122483533</v>
+        <v>122481479</v>
       </c>
       <c r="B22" t="n">
-        <v>78815</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3098,20 +3150,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1249</v>
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3121,13 +3178,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394737</v>
+        <v>394730</v>
       </c>
       <c r="R22" t="n">
-        <v>7062329</v>
+        <v>7062309</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3167,6 +3224,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
@@ -3181,22 +3243,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122483519</v>
+        <v>122481492</v>
       </c>
       <c r="B23" t="n">
-        <v>74753</v>
+        <v>79773</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3205,20 +3267,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6464</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,13 +3295,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394595</v>
+        <v>394589</v>
       </c>
       <c r="R23" t="n">
-        <v>7061889</v>
+        <v>7061895</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3275,25 +3342,30 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3303,7 +3375,7 @@
         <v>122483536</v>
       </c>
       <c r="B24" t="n">
-        <v>78815</v>
+        <v>78819</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,6 +3390,11 @@
       <c r="E24" t="n">
         <v>1249</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Platismatia norvegica</t>
@@ -3382,6 +3459,11 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
       <c r="AK24" t="inlineStr">
         <is>
           <t>Betula pubescens</t>
@@ -3400,17 +3482,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122483534</v>
+        <v>122483518</v>
       </c>
       <c r="B25" t="n">
-        <v>77588</v>
+        <v>78819</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3419,20 +3501,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6000248</v>
+        <v>1249</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3442,10 +3529,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394734</v>
+        <v>394636</v>
       </c>
       <c r="R25" t="n">
-        <v>7062334</v>
+        <v>7061901</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3486,9 +3573,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
@@ -3518,7 +3609,7 @@
         <v>122483521</v>
       </c>
       <c r="B26" t="n">
-        <v>94716</v>
+        <v>94729</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3532,6 +3623,11 @@
       </c>
       <c r="E26" t="n">
         <v>2668</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3617,10 +3713,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122481464</v>
+        <v>122483535</v>
       </c>
       <c r="B27" t="n">
-        <v>78736</v>
+        <v>78740</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3635,6 +3731,11 @@
       <c r="E27" t="n">
         <v>283</v>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Hypogymnia hultenii</t>
@@ -3652,13 +3753,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394733</v>
+        <v>394742</v>
       </c>
       <c r="R27" t="n">
-        <v>7062344</v>
+        <v>7062337</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3699,6 +3800,11 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK27" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3706,13 +3812,13 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3724,10 +3830,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122483537</v>
+        <v>122481464</v>
       </c>
       <c r="B28" t="n">
-        <v>78736</v>
+        <v>78740</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3742,6 +3848,11 @@
       <c r="E28" t="n">
         <v>283</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Hypogymnia hultenii</t>
@@ -3759,13 +3870,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394745</v>
+        <v>394733</v>
       </c>
       <c r="R28" t="n">
-        <v>7062367</v>
+        <v>7062344</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3806,6 +3917,11 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK28" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3813,28 +3929,28 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122483514</v>
+        <v>122483517</v>
       </c>
       <c r="B29" t="n">
-        <v>74758</v>
+        <v>74569</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3843,20 +3959,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>6428</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3866,10 +3987,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394834</v>
+        <v>394786</v>
       </c>
       <c r="R29" t="n">
-        <v>7062076</v>
+        <v>7061968</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3912,6 +4033,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
@@ -3938,10 +4064,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481483</v>
+        <v>122483534</v>
       </c>
       <c r="B30" t="n">
-        <v>57379</v>
+        <v>77592</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3950,41 +4076,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6000248</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394537</v>
+        <v>394734</v>
       </c>
       <c r="R30" t="n">
-        <v>7061922</v>
+        <v>7062334</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4016,24 +4142,35 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -4045,10 +4182,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481491</v>
+        <v>122481482</v>
       </c>
       <c r="B31" t="n">
-        <v>90831</v>
+        <v>78740</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4061,16 +4198,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>283</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4080,10 +4222,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394563</v>
+        <v>394669</v>
       </c>
       <c r="R31" t="n">
-        <v>7061882</v>
+        <v>7062253</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4127,6 +4269,11 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK31" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4134,7 +4281,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4152,10 +4299,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481495</v>
+        <v>122481491</v>
       </c>
       <c r="B32" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4168,16 +4315,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4187,10 +4339,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394826</v>
+        <v>394563</v>
       </c>
       <c r="R32" t="n">
-        <v>7062076</v>
+        <v>7061882</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,6 +4385,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
@@ -4259,10 +4416,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483516</v>
+        <v>122483529</v>
       </c>
       <c r="B33" t="n">
-        <v>79769</v>
+        <v>78819</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,20 +4428,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>1249</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4294,10 +4456,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394830</v>
+        <v>394652</v>
       </c>
       <c r="R33" t="n">
-        <v>7062019</v>
+        <v>7062221</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4338,18 +4500,22 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4367,10 +4533,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481482</v>
+        <v>122483519</v>
       </c>
       <c r="B34" t="n">
-        <v>78736</v>
+        <v>74757</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4383,16 +4549,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>283</v>
+        <v>6440</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4402,13 +4573,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394669</v>
+        <v>394595</v>
       </c>
       <c r="R34" t="n">
-        <v>7062253</v>
+        <v>7061889</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4449,6 +4620,11 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK34" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4456,28 +4632,28 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122483535</v>
+        <v>122481477</v>
       </c>
       <c r="B35" t="n">
-        <v>78736</v>
+        <v>78819</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,20 +4662,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>283</v>
+        <v>1249</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4509,13 +4690,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394742</v>
+        <v>394730</v>
       </c>
       <c r="R35" t="n">
-        <v>7062337</v>
+        <v>7062309</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4556,6 +4737,11 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK35" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4563,28 +4749,28 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122481466</v>
+        <v>122481475</v>
       </c>
       <c r="B36" t="n">
-        <v>74753</v>
+        <v>78912</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4593,20 +4779,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6459</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4616,10 +4807,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394746</v>
+        <v>394738</v>
       </c>
       <c r="R36" t="n">
-        <v>7062338</v>
+        <v>7062311</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4663,6 +4854,11 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK36" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4670,7 +4866,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4688,10 +4884,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483511</v>
+        <v>122481474</v>
       </c>
       <c r="B37" t="n">
-        <v>78736</v>
+        <v>57536</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4704,32 +4900,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>283</v>
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394793</v>
+        <v>394742</v>
       </c>
       <c r="R37" t="n">
-        <v>7062355</v>
+        <v>7062294</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4769,36 +4978,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481496</v>
+        <v>122483537</v>
       </c>
       <c r="B38" t="n">
-        <v>78815</v>
+        <v>78740</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4807,20 +5006,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1249</v>
+        <v>283</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4830,13 +5034,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394790</v>
+        <v>394745</v>
       </c>
       <c r="R38" t="n">
-        <v>7062334</v>
+        <v>7062367</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4877,6 +5081,11 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK38" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4884,13 +5093,13 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -4902,10 +5111,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122483529</v>
+        <v>122481483</v>
       </c>
       <c r="B39" t="n">
-        <v>78815</v>
+        <v>57383</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4914,36 +5123,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1249</v>
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394652</v>
+        <v>394537</v>
       </c>
       <c r="R39" t="n">
-        <v>7062221</v>
+        <v>7061922</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4975,6 +5194,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4983,36 +5207,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122481477</v>
+        <v>122481496</v>
       </c>
       <c r="B40" t="n">
-        <v>78815</v>
+        <v>78819</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5027,6 +5241,11 @@
       <c r="E40" t="n">
         <v>1249</v>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Platismatia norvegica</t>
@@ -5044,10 +5263,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394730</v>
+        <v>394790</v>
       </c>
       <c r="R40" t="n">
-        <v>7062309</v>
+        <v>7062334</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5091,6 +5310,11 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK40" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5098,7 +5322,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5116,10 +5340,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122483523</v>
+        <v>122481495</v>
       </c>
       <c r="B41" t="n">
-        <v>74748</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5132,16 +5356,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>310</v>
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5151,13 +5380,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394544</v>
+        <v>394826</v>
       </c>
       <c r="R41" t="n">
-        <v>7061898</v>
+        <v>7062076</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5195,9 +5424,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
@@ -5212,22 +5445,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481494</v>
+        <v>122481473</v>
       </c>
       <c r="B42" t="n">
-        <v>77589</v>
+        <v>78740</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5240,16 +5473,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>283</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5259,10 +5497,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394802</v>
+        <v>394712</v>
       </c>
       <c r="R42" t="n">
-        <v>7062015</v>
+        <v>7062279</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5306,6 +5544,11 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK42" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5313,7 +5556,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5331,10 +5574,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122483518</v>
+        <v>122481467</v>
       </c>
       <c r="B43" t="n">
-        <v>78815</v>
+        <v>77593</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5343,20 +5586,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1249</v>
+        <v>228579</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5366,13 +5614,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394636</v>
+        <v>394746</v>
       </c>
       <c r="R43" t="n">
-        <v>7061901</v>
+        <v>7062338</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5413,6 +5661,11 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK43" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5420,28 +5673,28 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481492</v>
+        <v>122481493</v>
       </c>
       <c r="B44" t="n">
-        <v>79769</v>
+        <v>78740</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5450,20 +5703,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>283</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5473,10 +5731,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394589</v>
+        <v>394812</v>
       </c>
       <c r="R44" t="n">
-        <v>7061895</v>
+        <v>7062006</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5520,14 +5778,19 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5545,10 +5808,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122481475</v>
+        <v>122483533</v>
       </c>
       <c r="B45" t="n">
-        <v>78908</v>
+        <v>78819</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5557,20 +5820,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6459</v>
+        <v>1249</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5580,13 +5848,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394738</v>
+        <v>394737</v>
       </c>
       <c r="R45" t="n">
-        <v>7062311</v>
+        <v>7062329</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5626,6 +5894,11 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
@@ -5640,7 +5913,7 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -5652,10 +5925,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122483517</v>
+        <v>122483514</v>
       </c>
       <c r="B46" t="n">
-        <v>74565</v>
+        <v>74762</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5664,20 +5937,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6428</v>
+        <v>1467</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5687,10 +5965,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394786</v>
+        <v>394834</v>
       </c>
       <c r="R46" t="n">
-        <v>7061968</v>
+        <v>7062076</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5733,6 +6011,11 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
@@ -5759,10 +6042,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122481474</v>
+        <v>122483511</v>
       </c>
       <c r="B47" t="n">
-        <v>57532</v>
+        <v>78740</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5775,40 +6058,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>283</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394742</v>
+        <v>394793</v>
       </c>
       <c r="R47" t="n">
-        <v>7062294</v>
+        <v>7062355</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5848,26 +6128,41 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122481473</v>
+        <v>122481466</v>
       </c>
       <c r="B48" t="n">
-        <v>78736</v>
+        <v>74757</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5880,16 +6175,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>283</v>
+        <v>6440</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5899,10 +6199,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394712</v>
+        <v>394746</v>
       </c>
       <c r="R48" t="n">
-        <v>7062279</v>
+        <v>7062338</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5946,6 +6246,11 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK48" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5953,7 +6258,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122481486</v>
+        <v>122481464</v>
       </c>
       <c r="B17" t="n">
-        <v>79738</v>
+        <v>78740</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394648</v>
+        <v>394733</v>
       </c>
       <c r="R17" t="n">
-        <v>7062211</v>
+        <v>7062344</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122483516</v>
+        <v>122483519</v>
       </c>
       <c r="B18" t="n">
-        <v>79773</v>
+        <v>74757</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,25 +2680,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394830</v>
+        <v>394595</v>
       </c>
       <c r="R18" t="n">
-        <v>7062019</v>
+        <v>7061889</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2752,23 +2752,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2786,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122481494</v>
+        <v>122483518</v>
       </c>
       <c r="B19" t="n">
-        <v>77593</v>
+        <v>78819</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2798,25 +2797,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2826,13 +2825,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394802</v>
+        <v>394636</v>
       </c>
       <c r="R19" t="n">
-        <v>7062015</v>
+        <v>7061901</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2885,28 +2884,28 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122483523</v>
+        <v>122481466</v>
       </c>
       <c r="B20" t="n">
-        <v>74752</v>
+        <v>74757</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2919,21 +2918,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>310</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2943,13 +2942,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394544</v>
+        <v>394746</v>
       </c>
       <c r="R20" t="n">
-        <v>7061898</v>
+        <v>7062338</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2987,7 +2986,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3003,28 +3001,28 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122483532</v>
+        <v>122481493</v>
       </c>
       <c r="B21" t="n">
-        <v>82443</v>
+        <v>78740</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3037,21 +3035,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3061,13 +3059,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394743</v>
+        <v>394812</v>
       </c>
       <c r="R21" t="n">
-        <v>7062322</v>
+        <v>7062006</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3120,13 +3118,13 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3138,10 +3136,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122481479</v>
+        <v>122483521</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>94742</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3150,25 +3148,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2668</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3178,13 +3176,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394730</v>
+        <v>394553</v>
       </c>
       <c r="R22" t="n">
-        <v>7062309</v>
+        <v>7061889</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3225,40 +3223,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122481492</v>
+        <v>122483514</v>
       </c>
       <c r="B23" t="n">
-        <v>79773</v>
+        <v>74762</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,25 +3255,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3295,13 +3283,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394589</v>
+        <v>394834</v>
       </c>
       <c r="R23" t="n">
-        <v>7061895</v>
+        <v>7062076</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3344,38 +3332,38 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122483536</v>
+        <v>122481494</v>
       </c>
       <c r="B24" t="n">
-        <v>78819</v>
+        <v>77593</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3384,25 +3372,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3412,13 +3400,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394745</v>
+        <v>394802</v>
       </c>
       <c r="R24" t="n">
-        <v>7062367</v>
+        <v>7062015</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3461,23 +3449,23 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3489,10 +3477,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122483518</v>
+        <v>122481479</v>
       </c>
       <c r="B25" t="n">
-        <v>78819</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3501,25 +3489,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3529,13 +3517,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394636</v>
+        <v>394730</v>
       </c>
       <c r="R25" t="n">
-        <v>7061901</v>
+        <v>7062309</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3594,22 +3582,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122483521</v>
+        <v>122481482</v>
       </c>
       <c r="B26" t="n">
-        <v>94729</v>
+        <v>78740</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3618,25 +3606,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2668</v>
+        <v>283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3646,13 +3634,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394553</v>
+        <v>394669</v>
       </c>
       <c r="R26" t="n">
-        <v>7061889</v>
+        <v>7062253</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3693,30 +3681,40 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122483535</v>
+        <v>122481486</v>
       </c>
       <c r="B27" t="n">
-        <v>78740</v>
+        <v>79738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3729,21 +3727,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>283</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3753,13 +3751,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394742</v>
+        <v>394648</v>
       </c>
       <c r="R27" t="n">
-        <v>7062337</v>
+        <v>7062211</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3812,13 +3810,13 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3830,10 +3828,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122481464</v>
+        <v>122481491</v>
       </c>
       <c r="B28" t="n">
-        <v>78740</v>
+        <v>90857</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3846,21 +3844,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3870,10 +3868,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394733</v>
+        <v>394563</v>
       </c>
       <c r="R28" t="n">
-        <v>7062344</v>
+        <v>7061882</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3929,7 +3927,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3947,10 +3945,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122483517</v>
+        <v>122481467</v>
       </c>
       <c r="B29" t="n">
-        <v>74569</v>
+        <v>77593</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3959,25 +3957,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3987,13 +3985,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394786</v>
+        <v>394746</v>
       </c>
       <c r="R29" t="n">
-        <v>7061968</v>
+        <v>7062338</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4046,28 +4044,28 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483534</v>
+        <v>122483523</v>
       </c>
       <c r="B30" t="n">
-        <v>77592</v>
+        <v>74752</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4076,25 +4074,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6000248</v>
+        <v>310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4104,10 +4102,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394734</v>
+        <v>394544</v>
       </c>
       <c r="R30" t="n">
-        <v>7062334</v>
+        <v>7061898</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4175,17 +4173,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481482</v>
+        <v>122481495</v>
       </c>
       <c r="B31" t="n">
-        <v>78740</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4198,21 +4196,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4222,10 +4220,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394669</v>
+        <v>394826</v>
       </c>
       <c r="R31" t="n">
-        <v>7062253</v>
+        <v>7062076</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4281,7 +4279,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4299,10 +4297,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481491</v>
+        <v>122483516</v>
       </c>
       <c r="B32" t="n">
-        <v>90844</v>
+        <v>79773</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4311,25 +4309,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4339,13 +4337,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394563</v>
+        <v>394830</v>
       </c>
       <c r="R32" t="n">
-        <v>7061882</v>
+        <v>7062019</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4383,40 +4381,41 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483529</v>
+        <v>122483536</v>
       </c>
       <c r="B33" t="n">
         <v>78819</v>
@@ -4456,10 +4455,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394652</v>
+        <v>394745</v>
       </c>
       <c r="R33" t="n">
-        <v>7062221</v>
+        <v>7062367</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4505,17 +4504,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4533,10 +4532,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122483519</v>
+        <v>122481483</v>
       </c>
       <c r="B34" t="n">
-        <v>74757</v>
+        <v>57383</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4549,37 +4548,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394595</v>
+        <v>394537</v>
       </c>
       <c r="R34" t="n">
-        <v>7061889</v>
+        <v>7061922</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4611,6 +4615,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4619,38 +4628,23 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122481477</v>
+        <v>122483533</v>
       </c>
       <c r="B35" t="n">
         <v>78819</v>
@@ -4690,13 +4684,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394730</v>
+        <v>394737</v>
       </c>
       <c r="R35" t="n">
-        <v>7062309</v>
+        <v>7062329</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4749,28 +4743,28 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122481475</v>
+        <v>122483511</v>
       </c>
       <c r="B36" t="n">
-        <v>78912</v>
+        <v>78740</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4779,25 +4773,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6459</v>
+        <v>283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4807,13 +4801,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394738</v>
+        <v>394793</v>
       </c>
       <c r="R36" t="n">
-        <v>7062311</v>
+        <v>7062355</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4872,22 +4866,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122481474</v>
+        <v>122483532</v>
       </c>
       <c r="B37" t="n">
-        <v>57536</v>
+        <v>82443</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4900,45 +4894,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394742</v>
+        <v>394743</v>
       </c>
       <c r="R37" t="n">
-        <v>7062294</v>
+        <v>7062322</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4978,26 +4964,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483537</v>
+        <v>122481492</v>
       </c>
       <c r="B38" t="n">
-        <v>78740</v>
+        <v>79773</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5006,25 +5007,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>283</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5034,13 +5035,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394745</v>
+        <v>394589</v>
       </c>
       <c r="R38" t="n">
-        <v>7062367</v>
+        <v>7061895</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5083,23 +5084,23 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5111,10 +5112,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481483</v>
+        <v>122483517</v>
       </c>
       <c r="B39" t="n">
-        <v>57383</v>
+        <v>74569</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5123,46 +5124,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394537</v>
+        <v>394786</v>
       </c>
       <c r="R39" t="n">
-        <v>7061922</v>
+        <v>7061968</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5194,11 +5190,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5207,26 +5198,41 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122481496</v>
+        <v>122483534</v>
       </c>
       <c r="B40" t="n">
-        <v>78819</v>
+        <v>77592</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5235,25 +5241,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1249</v>
+        <v>6000248</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5263,13 +5269,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394790</v>
+        <v>394734</v>
       </c>
       <c r="R40" t="n">
         <v>7062334</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5307,6 +5313,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5322,28 +5329,28 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122481495</v>
+        <v>122481475</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>78912</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5352,25 +5359,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5380,10 +5387,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394826</v>
+        <v>394738</v>
       </c>
       <c r="R41" t="n">
-        <v>7062076</v>
+        <v>7062311</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5457,10 +5464,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481473</v>
+        <v>122481496</v>
       </c>
       <c r="B42" t="n">
-        <v>78740</v>
+        <v>78819</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5469,25 +5476,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5497,10 +5504,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394712</v>
+        <v>394790</v>
       </c>
       <c r="R42" t="n">
-        <v>7062279</v>
+        <v>7062334</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5556,7 +5563,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5574,10 +5581,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481467</v>
+        <v>122483537</v>
       </c>
       <c r="B43" t="n">
-        <v>77593</v>
+        <v>78740</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5590,21 +5597,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5614,13 +5621,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394746</v>
+        <v>394745</v>
       </c>
       <c r="R43" t="n">
-        <v>7062338</v>
+        <v>7062367</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5673,25 +5680,25 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481493</v>
+        <v>122483535</v>
       </c>
       <c r="B44" t="n">
         <v>78740</v>
@@ -5731,13 +5738,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394812</v>
+        <v>394742</v>
       </c>
       <c r="R44" t="n">
-        <v>7062006</v>
+        <v>7062337</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5790,25 +5797,25 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122483533</v>
+        <v>122481477</v>
       </c>
       <c r="B45" t="n">
         <v>78819</v>
@@ -5848,13 +5855,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394737</v>
+        <v>394730</v>
       </c>
       <c r="R45" t="n">
-        <v>7062329</v>
+        <v>7062309</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5907,13 +5914,13 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -5925,10 +5932,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122483514</v>
+        <v>122481474</v>
       </c>
       <c r="B46" t="n">
-        <v>74762</v>
+        <v>57536</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5941,37 +5948,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394834</v>
+        <v>394742</v>
       </c>
       <c r="R46" t="n">
-        <v>7062076</v>
+        <v>7062294</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6011,38 +6026,23 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122483511</v>
+        <v>122481473</v>
       </c>
       <c r="B47" t="n">
         <v>78740</v>
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394793</v>
+        <v>394712</v>
       </c>
       <c r="R47" t="n">
-        <v>7062355</v>
+        <v>7062279</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6141,28 +6141,28 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122481466</v>
+        <v>122483529</v>
       </c>
       <c r="B48" t="n">
-        <v>74757</v>
+        <v>78819</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6171,25 +6171,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,13 +6199,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394746</v>
+        <v>394652</v>
       </c>
       <c r="R48" t="n">
-        <v>7062338</v>
+        <v>7062221</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6258,18 +6258,18 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122481464</v>
+        <v>122483519</v>
       </c>
       <c r="B17" t="n">
-        <v>78740</v>
+        <v>74757</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394733</v>
+        <v>394595</v>
       </c>
       <c r="R17" t="n">
-        <v>7062344</v>
+        <v>7061889</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,28 +2650,28 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122483519</v>
+        <v>122481464</v>
       </c>
       <c r="B18" t="n">
-        <v>74757</v>
+        <v>78740</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394595</v>
+        <v>394733</v>
       </c>
       <c r="R18" t="n">
-        <v>7061889</v>
+        <v>7062344</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,18 +2767,18 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122483514</v>
+        <v>122481494</v>
       </c>
       <c r="B23" t="n">
-        <v>74762</v>
+        <v>77593</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3259,21 +3259,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394834</v>
+        <v>394802</v>
       </c>
       <c r="R23" t="n">
-        <v>7062076</v>
+        <v>7062015</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3342,28 +3342,28 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122481494</v>
+        <v>122483514</v>
       </c>
       <c r="B24" t="n">
-        <v>77593</v>
+        <v>74762</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3376,21 +3376,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3400,13 +3400,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394802</v>
+        <v>394834</v>
       </c>
       <c r="R24" t="n">
-        <v>7062015</v>
+        <v>7062076</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3459,28 +3459,28 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122481479</v>
+        <v>122481482</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>78740</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394730</v>
+        <v>394669</v>
       </c>
       <c r="R25" t="n">
-        <v>7062309</v>
+        <v>7062253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481482</v>
+        <v>122481479</v>
       </c>
       <c r="B26" t="n">
-        <v>78740</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394669</v>
+        <v>394730</v>
       </c>
       <c r="R26" t="n">
-        <v>7062253</v>
+        <v>7062309</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122481467</v>
+        <v>122483523</v>
       </c>
       <c r="B29" t="n">
-        <v>77593</v>
+        <v>74752</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3961,21 +3961,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394746</v>
+        <v>394544</v>
       </c>
       <c r="R29" t="n">
-        <v>7062338</v>
+        <v>7061898</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4029,6 +4029,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4044,28 +4045,28 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483523</v>
+        <v>122481467</v>
       </c>
       <c r="B30" t="n">
-        <v>74752</v>
+        <v>77593</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4078,21 +4079,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>310</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4102,13 +4103,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394544</v>
+        <v>394746</v>
       </c>
       <c r="R30" t="n">
-        <v>7061898</v>
+        <v>7062338</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4146,7 +4147,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4162,18 +4162,18 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,7 +2551,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122483519</v>
+        <v>122481466</v>
       </c>
       <c r="B17" t="n">
         <v>74757</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394595</v>
+        <v>394746</v>
       </c>
       <c r="R17" t="n">
-        <v>7061889</v>
+        <v>7062338</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122481464</v>
+        <v>122483535</v>
       </c>
       <c r="B18" t="n">
         <v>78740</v>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394733</v>
+        <v>394742</v>
       </c>
       <c r="R18" t="n">
-        <v>7062344</v>
+        <v>7062337</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,28 +2767,28 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122483518</v>
+        <v>122481494</v>
       </c>
       <c r="B19" t="n">
-        <v>78819</v>
+        <v>77593</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394636</v>
+        <v>394802</v>
       </c>
       <c r="R19" t="n">
-        <v>7061901</v>
+        <v>7062015</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2884,25 +2884,25 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122481466</v>
+        <v>122483519</v>
       </c>
       <c r="B20" t="n">
         <v>74757</v>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394746</v>
+        <v>394595</v>
       </c>
       <c r="R20" t="n">
-        <v>7062338</v>
+        <v>7061889</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3001,28 +3001,28 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122481493</v>
+        <v>122483533</v>
       </c>
       <c r="B21" t="n">
-        <v>78740</v>
+        <v>78819</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394812</v>
+        <v>394737</v>
       </c>
       <c r="R21" t="n">
-        <v>7062006</v>
+        <v>7062329</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3118,28 +3118,28 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122483521</v>
+        <v>122483511</v>
       </c>
       <c r="B22" t="n">
-        <v>94742</v>
+        <v>78740</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3148,25 +3148,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2668</v>
+        <v>283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394553</v>
+        <v>394793</v>
       </c>
       <c r="R22" t="n">
-        <v>7061889</v>
+        <v>7062355</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3223,9 +3223,19 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3243,10 +3253,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122481494</v>
+        <v>122481464</v>
       </c>
       <c r="B23" t="n">
-        <v>77593</v>
+        <v>78740</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3259,21 +3269,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3283,10 +3293,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394802</v>
+        <v>394733</v>
       </c>
       <c r="R23" t="n">
-        <v>7062015</v>
+        <v>7062344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3342,7 +3352,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,10 +3487,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122481482</v>
+        <v>122481495</v>
       </c>
       <c r="B25" t="n">
-        <v>78740</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3493,21 +3503,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3517,10 +3527,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394669</v>
+        <v>394826</v>
       </c>
       <c r="R25" t="n">
-        <v>7062253</v>
+        <v>7062076</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3576,7 +3586,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3594,10 +3604,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481479</v>
+        <v>122483516</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>79773</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3606,25 +3616,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3634,13 +3644,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394730</v>
+        <v>394830</v>
       </c>
       <c r="R26" t="n">
-        <v>7062309</v>
+        <v>7062019</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3678,43 +3688,44 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122481486</v>
+        <v>122483521</v>
       </c>
       <c r="B27" t="n">
-        <v>79738</v>
+        <v>94742</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3723,25 +3734,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>2668</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3751,13 +3762,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394648</v>
+        <v>394553</v>
       </c>
       <c r="R27" t="n">
-        <v>7062211</v>
+        <v>7061889</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3798,40 +3809,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122481491</v>
+        <v>122483537</v>
       </c>
       <c r="B28" t="n">
-        <v>90857</v>
+        <v>78740</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3844,21 +3845,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3868,13 +3869,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394563</v>
+        <v>394745</v>
       </c>
       <c r="R28" t="n">
-        <v>7061882</v>
+        <v>7062367</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3933,22 +3934,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122483523</v>
+        <v>122481496</v>
       </c>
       <c r="B29" t="n">
-        <v>74752</v>
+        <v>78819</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3957,25 +3958,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>310</v>
+        <v>1249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3985,13 +3986,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394544</v>
+        <v>394790</v>
       </c>
       <c r="R29" t="n">
-        <v>7061898</v>
+        <v>7062334</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4029,7 +4030,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4045,28 +4045,28 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481467</v>
+        <v>122483534</v>
       </c>
       <c r="B30" t="n">
-        <v>77593</v>
+        <v>77592</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4075,25 +4075,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6000248</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4103,13 +4103,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394746</v>
+        <v>394734</v>
       </c>
       <c r="R30" t="n">
-        <v>7062338</v>
+        <v>7062334</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4147,6 +4147,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4162,28 +4163,28 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481495</v>
+        <v>122483523</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>74752</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4196,21 +4197,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4220,13 +4221,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394826</v>
+        <v>394544</v>
       </c>
       <c r="R31" t="n">
-        <v>7062076</v>
+        <v>7061898</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4264,6 +4265,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4285,22 +4287,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122483516</v>
+        <v>122481482</v>
       </c>
       <c r="B32" t="n">
-        <v>79773</v>
+        <v>78740</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4309,25 +4311,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4337,13 +4339,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394830</v>
+        <v>394669</v>
       </c>
       <c r="R32" t="n">
-        <v>7062019</v>
+        <v>7062253</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4381,44 +4383,43 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483536</v>
+        <v>122481467</v>
       </c>
       <c r="B33" t="n">
-        <v>78819</v>
+        <v>77593</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4427,25 +4428,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4455,13 +4456,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394745</v>
+        <v>394746</v>
       </c>
       <c r="R33" t="n">
-        <v>7062367</v>
+        <v>7062338</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4504,38 +4505,38 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481483</v>
+        <v>122481493</v>
       </c>
       <c r="B34" t="n">
-        <v>57383</v>
+        <v>78740</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4548,39 +4549,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394537</v>
+        <v>394812</v>
       </c>
       <c r="R34" t="n">
-        <v>7061922</v>
+        <v>7062006</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4615,11 +4611,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4628,6 +4619,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4644,7 +4650,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122483533</v>
+        <v>122483529</v>
       </c>
       <c r="B35" t="n">
         <v>78819</v>
@@ -4684,10 +4690,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394737</v>
+        <v>394652</v>
       </c>
       <c r="R35" t="n">
-        <v>7062329</v>
+        <v>7062221</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4761,10 +4767,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122483511</v>
+        <v>122481492</v>
       </c>
       <c r="B36" t="n">
-        <v>78740</v>
+        <v>79773</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4773,25 +4779,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>283</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4801,13 +4807,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394793</v>
+        <v>394589</v>
       </c>
       <c r="R36" t="n">
-        <v>7062355</v>
+        <v>7061895</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4850,38 +4856,38 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483532</v>
+        <v>122481477</v>
       </c>
       <c r="B37" t="n">
-        <v>82443</v>
+        <v>78819</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4890,25 +4896,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>1249</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4918,13 +4924,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394743</v>
+        <v>394730</v>
       </c>
       <c r="R37" t="n">
-        <v>7062322</v>
+        <v>7062309</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4977,28 +4983,28 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481492</v>
+        <v>122483518</v>
       </c>
       <c r="B38" t="n">
-        <v>79773</v>
+        <v>78819</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5007,25 +5013,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5035,13 +5041,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394589</v>
+        <v>394636</v>
       </c>
       <c r="R38" t="n">
-        <v>7061895</v>
+        <v>7061901</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5084,38 +5090,38 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122483517</v>
+        <v>122481491</v>
       </c>
       <c r="B39" t="n">
-        <v>74569</v>
+        <v>90857</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,25 +5130,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6428</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5152,13 +5158,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394786</v>
+        <v>394563</v>
       </c>
       <c r="R39" t="n">
-        <v>7061968</v>
+        <v>7061882</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5217,22 +5223,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122483534</v>
+        <v>122481475</v>
       </c>
       <c r="B40" t="n">
-        <v>77592</v>
+        <v>78912</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5241,25 +5247,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6000248</v>
+        <v>6459</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5269,13 +5275,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394734</v>
+        <v>394738</v>
       </c>
       <c r="R40" t="n">
-        <v>7062334</v>
+        <v>7062311</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5313,7 +5319,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5335,22 +5340,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122481475</v>
+        <v>122481483</v>
       </c>
       <c r="B41" t="n">
-        <v>78912</v>
+        <v>57383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5359,38 +5364,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394738</v>
+        <v>394537</v>
       </c>
       <c r="R41" t="n">
-        <v>7062311</v>
+        <v>7061922</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5425,6 +5435,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5433,21 +5448,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5464,10 +5464,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481496</v>
+        <v>122483517</v>
       </c>
       <c r="B42" t="n">
-        <v>78819</v>
+        <v>74569</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5476,25 +5476,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1249</v>
+        <v>6428</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5504,13 +5504,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394790</v>
+        <v>394786</v>
       </c>
       <c r="R42" t="n">
-        <v>7062334</v>
+        <v>7061968</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5563,28 +5563,28 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122483537</v>
+        <v>122481479</v>
       </c>
       <c r="B43" t="n">
-        <v>78740</v>
+        <v>78656</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5597,21 +5597,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5621,13 +5621,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394745</v>
+        <v>394730</v>
       </c>
       <c r="R43" t="n">
-        <v>7062367</v>
+        <v>7062309</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5686,22 +5686,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122483535</v>
+        <v>122481486</v>
       </c>
       <c r="B44" t="n">
-        <v>78740</v>
+        <v>79738</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5714,21 +5714,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>283</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5738,13 +5738,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394742</v>
+        <v>394648</v>
       </c>
       <c r="R44" t="n">
-        <v>7062337</v>
+        <v>7062211</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5797,28 +5797,28 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122481477</v>
+        <v>122481474</v>
       </c>
       <c r="B45" t="n">
-        <v>78819</v>
+        <v>57536</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5827,38 +5827,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1249</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394730</v>
+        <v>394742</v>
       </c>
       <c r="R45" t="n">
-        <v>7062309</v>
+        <v>7062294</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5901,21 +5909,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>grenar på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5932,10 +5925,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122481474</v>
+        <v>122483532</v>
       </c>
       <c r="B46" t="n">
-        <v>57536</v>
+        <v>82443</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5948,45 +5941,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394742</v>
+        <v>394743</v>
       </c>
       <c r="R46" t="n">
-        <v>7062294</v>
+        <v>7062322</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6026,26 +6011,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122481473</v>
+        <v>122483536</v>
       </c>
       <c r="B47" t="n">
-        <v>78740</v>
+        <v>78819</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6054,25 +6054,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394712</v>
+        <v>394745</v>
       </c>
       <c r="R47" t="n">
-        <v>7062279</v>
+        <v>7062367</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6131,38 +6131,38 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122483529</v>
+        <v>122481473</v>
       </c>
       <c r="B48" t="n">
-        <v>78819</v>
+        <v>78740</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6171,25 +6171,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,13 +6199,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394652</v>
+        <v>394712</v>
       </c>
       <c r="R48" t="n">
-        <v>7062221</v>
+        <v>7062279</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6258,18 +6258,18 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122481466</v>
+        <v>122483532</v>
       </c>
       <c r="B17" t="n">
-        <v>74757</v>
+        <v>82443</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394746</v>
+        <v>394743</v>
       </c>
       <c r="R17" t="n">
-        <v>7062338</v>
+        <v>7062322</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,28 +2650,28 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122483535</v>
+        <v>122481479</v>
       </c>
       <c r="B18" t="n">
-        <v>78740</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394742</v>
+        <v>394730</v>
       </c>
       <c r="R18" t="n">
-        <v>7062337</v>
+        <v>7062309</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2773,22 +2773,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122481494</v>
+        <v>122481492</v>
       </c>
       <c r="B19" t="n">
-        <v>77593</v>
+        <v>79773</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394802</v>
+        <v>394589</v>
       </c>
       <c r="R19" t="n">
-        <v>7062015</v>
+        <v>7061895</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2874,17 +2874,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122483519</v>
+        <v>122483536</v>
       </c>
       <c r="B20" t="n">
-        <v>74757</v>
+        <v>78819</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2914,25 +2914,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394595</v>
+        <v>394745</v>
       </c>
       <c r="R20" t="n">
-        <v>7061889</v>
+        <v>7062367</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2991,17 +2991,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122483533</v>
+        <v>122483529</v>
       </c>
       <c r="B21" t="n">
         <v>78819</v>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394737</v>
+        <v>394652</v>
       </c>
       <c r="R21" t="n">
-        <v>7062329</v>
+        <v>7062221</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122483511</v>
+        <v>122481491</v>
       </c>
       <c r="B22" t="n">
-        <v>78740</v>
+        <v>90851</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3152,21 +3152,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394793</v>
+        <v>394563</v>
       </c>
       <c r="R22" t="n">
-        <v>7062355</v>
+        <v>7061882</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3241,19 +3241,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122481464</v>
+        <v>122483537</v>
       </c>
       <c r="B23" t="n">
         <v>78740</v>
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394733</v>
+        <v>394745</v>
       </c>
       <c r="R23" t="n">
-        <v>7062344</v>
+        <v>7062367</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3352,28 +3352,28 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122483514</v>
+        <v>122481496</v>
       </c>
       <c r="B24" t="n">
-        <v>74762</v>
+        <v>78819</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3382,25 +3382,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394834</v>
+        <v>394790</v>
       </c>
       <c r="R24" t="n">
-        <v>7062076</v>
+        <v>7062334</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3469,28 +3469,28 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122481495</v>
+        <v>122481466</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3503,21 +3503,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394826</v>
+        <v>394746</v>
       </c>
       <c r="R25" t="n">
-        <v>7062076</v>
+        <v>7062338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122483516</v>
+        <v>122481486</v>
       </c>
       <c r="B26" t="n">
-        <v>79773</v>
+        <v>79738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3616,25 +3616,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3644,13 +3644,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394830</v>
+        <v>394648</v>
       </c>
       <c r="R26" t="n">
-        <v>7062019</v>
+        <v>7062211</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3688,44 +3688,43 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122483521</v>
+        <v>122483534</v>
       </c>
       <c r="B27" t="n">
-        <v>94742</v>
+        <v>77592</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3734,25 +3733,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2668</v>
+        <v>6000248</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3762,10 +3761,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394553</v>
+        <v>394734</v>
       </c>
       <c r="R27" t="n">
-        <v>7061889</v>
+        <v>7062334</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3806,12 +3805,23 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3829,7 +3839,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122483537</v>
+        <v>122481482</v>
       </c>
       <c r="B28" t="n">
         <v>78740</v>
@@ -3869,13 +3879,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394745</v>
+        <v>394669</v>
       </c>
       <c r="R28" t="n">
-        <v>7062367</v>
+        <v>7062253</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3928,28 +3938,28 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122481496</v>
+        <v>122481475</v>
       </c>
       <c r="B29" t="n">
-        <v>78819</v>
+        <v>78912</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3958,25 +3968,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1249</v>
+        <v>6459</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3986,10 +3996,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394790</v>
+        <v>394738</v>
       </c>
       <c r="R29" t="n">
-        <v>7062334</v>
+        <v>7062311</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4045,7 +4055,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4063,10 +4073,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483534</v>
+        <v>122483516</v>
       </c>
       <c r="B30" t="n">
-        <v>77592</v>
+        <v>79773</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4075,25 +4085,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6000248</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4103,10 +4113,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394734</v>
+        <v>394830</v>
       </c>
       <c r="R30" t="n">
-        <v>7062334</v>
+        <v>7062019</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4153,17 +4163,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4181,10 +4191,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122483523</v>
+        <v>122481464</v>
       </c>
       <c r="B31" t="n">
-        <v>74752</v>
+        <v>78740</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4197,21 +4207,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4221,13 +4231,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394544</v>
+        <v>394733</v>
       </c>
       <c r="R31" t="n">
-        <v>7061898</v>
+        <v>7062344</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4265,7 +4275,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4281,28 +4290,28 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481482</v>
+        <v>122483533</v>
       </c>
       <c r="B32" t="n">
-        <v>78740</v>
+        <v>78819</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4311,25 +4320,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4339,13 +4348,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394669</v>
+        <v>394737</v>
       </c>
       <c r="R32" t="n">
-        <v>7062253</v>
+        <v>7062329</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4398,28 +4407,28 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122481467</v>
+        <v>122481495</v>
       </c>
       <c r="B33" t="n">
-        <v>77593</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4432,21 +4441,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4456,10 +4465,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394746</v>
+        <v>394826</v>
       </c>
       <c r="R33" t="n">
-        <v>7062338</v>
+        <v>7062076</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4515,7 +4524,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4533,10 +4542,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481493</v>
+        <v>122483514</v>
       </c>
       <c r="B34" t="n">
-        <v>78740</v>
+        <v>74762</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4549,21 +4558,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>283</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4573,13 +4582,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394812</v>
+        <v>394834</v>
       </c>
       <c r="R34" t="n">
-        <v>7062006</v>
+        <v>7062076</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4632,28 +4641,28 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122483529</v>
+        <v>122481483</v>
       </c>
       <c r="B35" t="n">
-        <v>78819</v>
+        <v>57383</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4662,41 +4671,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394652</v>
+        <v>394537</v>
       </c>
       <c r="R35" t="n">
-        <v>7062221</v>
+        <v>7061922</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4728,6 +4742,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4736,41 +4755,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122481492</v>
+        <v>122483518</v>
       </c>
       <c r="B36" t="n">
-        <v>79773</v>
+        <v>78819</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4779,25 +4783,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4807,13 +4811,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394589</v>
+        <v>394636</v>
       </c>
       <c r="R36" t="n">
-        <v>7061895</v>
+        <v>7061901</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4856,38 +4860,38 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122481477</v>
+        <v>122483511</v>
       </c>
       <c r="B37" t="n">
-        <v>78819</v>
+        <v>78740</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4896,25 +4900,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4924,13 +4928,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394730</v>
+        <v>394793</v>
       </c>
       <c r="R37" t="n">
-        <v>7062309</v>
+        <v>7062355</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4983,28 +4987,28 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483518</v>
+        <v>122481494</v>
       </c>
       <c r="B38" t="n">
-        <v>78819</v>
+        <v>77593</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5013,25 +5017,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5041,13 +5045,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394636</v>
+        <v>394802</v>
       </c>
       <c r="R38" t="n">
-        <v>7061901</v>
+        <v>7062015</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5100,28 +5104,28 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481491</v>
+        <v>122483521</v>
       </c>
       <c r="B39" t="n">
-        <v>90857</v>
+        <v>94744</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5130,25 +5134,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>2668</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5158,13 +5162,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394563</v>
+        <v>394553</v>
       </c>
       <c r="R39" t="n">
-        <v>7061882</v>
+        <v>7061889</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5205,40 +5209,30 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122481475</v>
+        <v>122481493</v>
       </c>
       <c r="B40" t="n">
-        <v>78912</v>
+        <v>78740</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5247,25 +5241,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6459</v>
+        <v>283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5275,10 +5269,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394738</v>
+        <v>394812</v>
       </c>
       <c r="R40" t="n">
-        <v>7062311</v>
+        <v>7062006</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5334,7 +5328,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5352,10 +5346,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122481483</v>
+        <v>122483535</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>78740</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5368,42 +5362,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394537</v>
+        <v>394742</v>
       </c>
       <c r="R41" t="n">
-        <v>7061922</v>
+        <v>7062337</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5435,11 +5424,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5448,26 +5432,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122483517</v>
+        <v>122481474</v>
       </c>
       <c r="B42" t="n">
-        <v>74569</v>
+        <v>57536</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5476,41 +5475,49 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6428</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394786</v>
+        <v>394742</v>
       </c>
       <c r="R42" t="n">
-        <v>7061968</v>
+        <v>7062294</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5550,41 +5557,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481479</v>
+        <v>122481467</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>77593</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5597,21 +5589,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5621,10 +5613,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394730</v>
+        <v>394746</v>
       </c>
       <c r="R43" t="n">
-        <v>7062309</v>
+        <v>7062338</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5680,7 +5672,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5698,10 +5690,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481486</v>
+        <v>122481473</v>
       </c>
       <c r="B44" t="n">
-        <v>79738</v>
+        <v>78740</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5714,21 +5706,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5738,10 +5730,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394648</v>
+        <v>394712</v>
       </c>
       <c r="R44" t="n">
-        <v>7062211</v>
+        <v>7062279</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5797,7 +5789,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5815,10 +5807,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122481474</v>
+        <v>122483519</v>
       </c>
       <c r="B45" t="n">
-        <v>57536</v>
+        <v>74757</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5831,45 +5823,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394742</v>
+        <v>394595</v>
       </c>
       <c r="R45" t="n">
-        <v>7062294</v>
+        <v>7061889</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5909,26 +5893,41 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122483532</v>
+        <v>122483517</v>
       </c>
       <c r="B46" t="n">
-        <v>82443</v>
+        <v>74569</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5937,25 +5936,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6428</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5965,10 +5964,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394743</v>
+        <v>394786</v>
       </c>
       <c r="R46" t="n">
-        <v>7062322</v>
+        <v>7061968</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -6042,7 +6041,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122483536</v>
+        <v>122481477</v>
       </c>
       <c r="B47" t="n">
         <v>78819</v>
@@ -6082,13 +6081,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394745</v>
+        <v>394730</v>
       </c>
       <c r="R47" t="n">
-        <v>7062367</v>
+        <v>7062309</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6131,38 +6130,38 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122481473</v>
+        <v>122483523</v>
       </c>
       <c r="B48" t="n">
-        <v>78740</v>
+        <v>74752</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6175,21 +6174,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,13 +6198,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394712</v>
+        <v>394544</v>
       </c>
       <c r="R48" t="n">
-        <v>7062279</v>
+        <v>7061898</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6243,6 +6242,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6258,18 +6258,18 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122483532</v>
+        <v>122481466</v>
       </c>
       <c r="B17" t="n">
-        <v>82443</v>
+        <v>74757</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394743</v>
+        <v>394746</v>
       </c>
       <c r="R17" t="n">
-        <v>7062322</v>
+        <v>7062338</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,28 +2650,28 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122481479</v>
+        <v>122481473</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>78740</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394730</v>
+        <v>394712</v>
       </c>
       <c r="R18" t="n">
-        <v>7062309</v>
+        <v>7062279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122481492</v>
+        <v>122481486</v>
       </c>
       <c r="B19" t="n">
-        <v>79773</v>
+        <v>79738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394589</v>
+        <v>394648</v>
       </c>
       <c r="R19" t="n">
-        <v>7061895</v>
+        <v>7062211</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2874,17 +2874,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122483536</v>
+        <v>122481464</v>
       </c>
       <c r="B20" t="n">
-        <v>78819</v>
+        <v>78740</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2914,25 +2914,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394745</v>
+        <v>394733</v>
       </c>
       <c r="R20" t="n">
-        <v>7062367</v>
+        <v>7062344</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2991,38 +2991,38 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122483529</v>
+        <v>122481474</v>
       </c>
       <c r="B21" t="n">
-        <v>78819</v>
+        <v>57536</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3031,41 +3031,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1249</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394652</v>
+        <v>394742</v>
       </c>
       <c r="R21" t="n">
-        <v>7062221</v>
+        <v>7062294</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3105,41 +3113,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122481491</v>
+        <v>122483533</v>
       </c>
       <c r="B22" t="n">
-        <v>90851</v>
+        <v>78819</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3148,25 +3141,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3176,13 +3169,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394563</v>
+        <v>394737</v>
       </c>
       <c r="R22" t="n">
-        <v>7061882</v>
+        <v>7062329</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3241,22 +3234,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122483537</v>
+        <v>122481467</v>
       </c>
       <c r="B23" t="n">
-        <v>78740</v>
+        <v>77593</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3269,21 +3262,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3293,13 +3286,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394745</v>
+        <v>394746</v>
       </c>
       <c r="R23" t="n">
-        <v>7062367</v>
+        <v>7062338</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3352,28 +3345,28 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122481496</v>
+        <v>122483521</v>
       </c>
       <c r="B24" t="n">
-        <v>78819</v>
+        <v>94744</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3382,25 +3375,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1249</v>
+        <v>2668</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3410,13 +3403,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394790</v>
+        <v>394553</v>
       </c>
       <c r="R24" t="n">
-        <v>7062334</v>
+        <v>7061889</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3457,40 +3450,30 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122481466</v>
+        <v>122483517</v>
       </c>
       <c r="B25" t="n">
-        <v>74757</v>
+        <v>74569</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3499,25 +3482,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3527,13 +3510,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394746</v>
+        <v>394786</v>
       </c>
       <c r="R25" t="n">
-        <v>7062338</v>
+        <v>7061968</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3586,28 +3569,28 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481486</v>
+        <v>122483536</v>
       </c>
       <c r="B26" t="n">
-        <v>79738</v>
+        <v>78819</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3616,25 +3599,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3644,13 +3627,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394648</v>
+        <v>394745</v>
       </c>
       <c r="R26" t="n">
-        <v>7062211</v>
+        <v>7062367</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3693,38 +3676,38 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122483534</v>
+        <v>122483514</v>
       </c>
       <c r="B27" t="n">
-        <v>77592</v>
+        <v>74762</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3733,25 +3716,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6000248</v>
+        <v>1467</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3761,10 +3744,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394734</v>
+        <v>394834</v>
       </c>
       <c r="R27" t="n">
-        <v>7062334</v>
+        <v>7062076</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3805,7 +3788,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3839,10 +3821,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122481482</v>
+        <v>122481496</v>
       </c>
       <c r="B28" t="n">
-        <v>78740</v>
+        <v>78819</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3851,25 +3833,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3879,10 +3861,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394669</v>
+        <v>394790</v>
       </c>
       <c r="R28" t="n">
-        <v>7062253</v>
+        <v>7062334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3938,7 +3920,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4073,10 +4055,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483516</v>
+        <v>122483523</v>
       </c>
       <c r="B30" t="n">
-        <v>79773</v>
+        <v>74752</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4085,25 +4067,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4113,10 +4095,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394830</v>
+        <v>394544</v>
       </c>
       <c r="R30" t="n">
-        <v>7062019</v>
+        <v>7061898</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4163,17 +4145,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4191,10 +4173,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481464</v>
+        <v>122481477</v>
       </c>
       <c r="B31" t="n">
-        <v>78740</v>
+        <v>78819</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4203,25 +4185,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4231,10 +4213,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394733</v>
+        <v>394730</v>
       </c>
       <c r="R31" t="n">
-        <v>7062344</v>
+        <v>7062309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4290,7 +4272,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4308,10 +4290,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122483533</v>
+        <v>122481492</v>
       </c>
       <c r="B32" t="n">
-        <v>78819</v>
+        <v>79773</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4320,25 +4302,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4348,13 +4330,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394737</v>
+        <v>394589</v>
       </c>
       <c r="R32" t="n">
-        <v>7062329</v>
+        <v>7061895</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4397,38 +4379,38 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122481495</v>
+        <v>122481494</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>77593</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4441,21 +4423,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4465,10 +4447,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394826</v>
+        <v>394802</v>
       </c>
       <c r="R33" t="n">
-        <v>7062076</v>
+        <v>7062015</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4524,7 +4506,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4542,10 +4524,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122483514</v>
+        <v>122481491</v>
       </c>
       <c r="B34" t="n">
-        <v>74762</v>
+        <v>90851</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4558,21 +4540,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4582,13 +4564,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394834</v>
+        <v>394563</v>
       </c>
       <c r="R34" t="n">
-        <v>7062076</v>
+        <v>7061882</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4647,22 +4629,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122481483</v>
+        <v>122483511</v>
       </c>
       <c r="B35" t="n">
-        <v>57383</v>
+        <v>78740</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4675,42 +4657,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394537</v>
+        <v>394793</v>
       </c>
       <c r="R35" t="n">
-        <v>7061922</v>
+        <v>7062355</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4742,11 +4719,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4755,23 +4727,38 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122483518</v>
+        <v>122483529</v>
       </c>
       <c r="B36" t="n">
         <v>78819</v>
@@ -4811,10 +4798,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394636</v>
+        <v>394652</v>
       </c>
       <c r="R36" t="n">
-        <v>7061901</v>
+        <v>7062221</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4888,10 +4875,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483511</v>
+        <v>122483516</v>
       </c>
       <c r="B37" t="n">
-        <v>78740</v>
+        <v>79773</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4900,25 +4887,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>283</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4928,10 +4915,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394793</v>
+        <v>394830</v>
       </c>
       <c r="R37" t="n">
-        <v>7062355</v>
+        <v>7062019</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4972,22 +4959,23 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5005,10 +4993,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481494</v>
+        <v>122483519</v>
       </c>
       <c r="B38" t="n">
-        <v>77593</v>
+        <v>74757</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5021,21 +5009,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5045,13 +5033,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394802</v>
+        <v>394595</v>
       </c>
       <c r="R38" t="n">
-        <v>7062015</v>
+        <v>7061889</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5104,28 +5092,28 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122483521</v>
+        <v>122483518</v>
       </c>
       <c r="B39" t="n">
-        <v>94744</v>
+        <v>78819</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5134,25 +5122,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2668</v>
+        <v>1249</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5162,10 +5150,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394553</v>
+        <v>394636</v>
       </c>
       <c r="R39" t="n">
-        <v>7061889</v>
+        <v>7061901</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5209,9 +5197,19 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5229,7 +5227,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122481493</v>
+        <v>122483537</v>
       </c>
       <c r="B40" t="n">
         <v>78740</v>
@@ -5269,13 +5267,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394812</v>
+        <v>394745</v>
       </c>
       <c r="R40" t="n">
-        <v>7062006</v>
+        <v>7062367</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5328,28 +5326,28 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122483535</v>
+        <v>122483534</v>
       </c>
       <c r="B41" t="n">
-        <v>78740</v>
+        <v>77592</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5358,25 +5356,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>283</v>
+        <v>6000248</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5386,10 +5384,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394742</v>
+        <v>394734</v>
       </c>
       <c r="R41" t="n">
-        <v>7062337</v>
+        <v>7062334</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5430,6 +5428,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5463,10 +5462,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481474</v>
+        <v>122483532</v>
       </c>
       <c r="B42" t="n">
-        <v>57536</v>
+        <v>82443</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5479,45 +5478,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394742</v>
+        <v>394743</v>
       </c>
       <c r="R42" t="n">
-        <v>7062294</v>
+        <v>7062322</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5557,26 +5548,41 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481467</v>
+        <v>122481495</v>
       </c>
       <c r="B43" t="n">
-        <v>77593</v>
+        <v>78656</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5589,21 +5595,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5613,10 +5619,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394746</v>
+        <v>394826</v>
       </c>
       <c r="R43" t="n">
-        <v>7062338</v>
+        <v>7062076</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5672,7 +5678,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5690,7 +5696,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481473</v>
+        <v>122481482</v>
       </c>
       <c r="B44" t="n">
         <v>78740</v>
@@ -5730,10 +5736,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394712</v>
+        <v>394669</v>
       </c>
       <c r="R44" t="n">
-        <v>7062279</v>
+        <v>7062253</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5807,10 +5813,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122483519</v>
+        <v>122481483</v>
       </c>
       <c r="B45" t="n">
-        <v>74757</v>
+        <v>57383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5823,37 +5829,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394595</v>
+        <v>394537</v>
       </c>
       <c r="R45" t="n">
-        <v>7061889</v>
+        <v>7061922</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5885,6 +5896,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5893,41 +5909,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122483517</v>
+        <v>122481479</v>
       </c>
       <c r="B46" t="n">
-        <v>74569</v>
+        <v>78656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5936,25 +5937,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5964,13 +5965,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394786</v>
+        <v>394730</v>
       </c>
       <c r="R46" t="n">
-        <v>7061968</v>
+        <v>7062309</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6029,22 +6030,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122481477</v>
+        <v>122481493</v>
       </c>
       <c r="B47" t="n">
-        <v>78819</v>
+        <v>78740</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6053,25 +6054,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6081,10 +6082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394730</v>
+        <v>394812</v>
       </c>
       <c r="R47" t="n">
-        <v>7062309</v>
+        <v>7062006</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6140,7 +6141,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6158,10 +6159,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122483523</v>
+        <v>122483535</v>
       </c>
       <c r="B48" t="n">
-        <v>74752</v>
+        <v>78740</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6174,21 +6175,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6198,10 +6199,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394544</v>
+        <v>394742</v>
       </c>
       <c r="R48" t="n">
-        <v>7061898</v>
+        <v>7062337</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6242,7 +6243,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122481466</v>
+        <v>122483536</v>
       </c>
       <c r="B17" t="n">
-        <v>74757</v>
+        <v>78820</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394746</v>
+        <v>394745</v>
       </c>
       <c r="R17" t="n">
-        <v>7062338</v>
+        <v>7062367</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2640,38 +2640,38 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122481473</v>
+        <v>122481492</v>
       </c>
       <c r="B18" t="n">
-        <v>78740</v>
+        <v>79774</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,25 +2680,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394712</v>
+        <v>394589</v>
       </c>
       <c r="R18" t="n">
-        <v>7062279</v>
+        <v>7061895</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2757,17 +2757,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122481486</v>
+        <v>122481479</v>
       </c>
       <c r="B19" t="n">
-        <v>79738</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394648</v>
+        <v>394730</v>
       </c>
       <c r="R19" t="n">
-        <v>7062211</v>
+        <v>7062309</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122481464</v>
+        <v>122481486</v>
       </c>
       <c r="B20" t="n">
-        <v>78740</v>
+        <v>79739</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>283</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394733</v>
+        <v>394648</v>
       </c>
       <c r="R20" t="n">
-        <v>7062344</v>
+        <v>7062211</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122481474</v>
+        <v>122483532</v>
       </c>
       <c r="B21" t="n">
-        <v>57536</v>
+        <v>82444</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3035,45 +3035,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394742</v>
+        <v>394743</v>
       </c>
       <c r="R21" t="n">
-        <v>7062294</v>
+        <v>7062322</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3113,26 +3105,41 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122483533</v>
+        <v>122483521</v>
       </c>
       <c r="B22" t="n">
-        <v>78819</v>
+        <v>94745</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3141,25 +3148,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1249</v>
+        <v>2668</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3169,10 +3176,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394737</v>
+        <v>394553</v>
       </c>
       <c r="R22" t="n">
-        <v>7062329</v>
+        <v>7061889</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3216,19 +3223,9 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3246,10 +3243,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122481467</v>
+        <v>122483519</v>
       </c>
       <c r="B23" t="n">
-        <v>77593</v>
+        <v>74758</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3262,21 +3259,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3286,13 +3283,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394746</v>
+        <v>394595</v>
       </c>
       <c r="R23" t="n">
-        <v>7062338</v>
+        <v>7061889</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3345,28 +3342,28 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122483521</v>
+        <v>122483535</v>
       </c>
       <c r="B24" t="n">
-        <v>94744</v>
+        <v>78741</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3375,25 +3372,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2668</v>
+        <v>283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3403,10 +3400,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394553</v>
+        <v>394742</v>
       </c>
       <c r="R24" t="n">
-        <v>7061889</v>
+        <v>7062337</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3450,9 +3447,19 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3473,7 +3480,7 @@
         <v>122483517</v>
       </c>
       <c r="B25" t="n">
-        <v>74569</v>
+        <v>74570</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3587,10 +3594,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122483536</v>
+        <v>122481467</v>
       </c>
       <c r="B26" t="n">
-        <v>78819</v>
+        <v>77594</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3599,25 +3606,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3627,13 +3634,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394745</v>
+        <v>394746</v>
       </c>
       <c r="R26" t="n">
-        <v>7062367</v>
+        <v>7062338</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3676,38 +3683,38 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122483514</v>
+        <v>122483523</v>
       </c>
       <c r="B27" t="n">
-        <v>74762</v>
+        <v>74753</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3720,21 +3727,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1467</v>
+        <v>310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3744,10 +3751,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394834</v>
+        <v>394544</v>
       </c>
       <c r="R27" t="n">
-        <v>7062076</v>
+        <v>7061898</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3788,6 +3795,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3821,10 +3829,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122481496</v>
+        <v>122483511</v>
       </c>
       <c r="B28" t="n">
-        <v>78819</v>
+        <v>78741</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3833,25 +3841,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3861,13 +3869,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394790</v>
+        <v>394793</v>
       </c>
       <c r="R28" t="n">
-        <v>7062334</v>
+        <v>7062355</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3920,28 +3928,28 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122481475</v>
+        <v>122481477</v>
       </c>
       <c r="B29" t="n">
-        <v>78912</v>
+        <v>78820</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3950,25 +3958,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6459</v>
+        <v>1249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3978,10 +3986,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394738</v>
+        <v>394730</v>
       </c>
       <c r="R29" t="n">
-        <v>7062311</v>
+        <v>7062309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4037,7 +4045,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4055,10 +4063,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483523</v>
+        <v>122481474</v>
       </c>
       <c r="B30" t="n">
-        <v>74752</v>
+        <v>57537</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4071,37 +4079,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>310</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394544</v>
+        <v>394742</v>
       </c>
       <c r="R30" t="n">
-        <v>7061898</v>
+        <v>7062294</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4139,44 +4155,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481477</v>
+        <v>122481475</v>
       </c>
       <c r="B31" t="n">
-        <v>78819</v>
+        <v>78913</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4185,25 +4185,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1249</v>
+        <v>6459</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394730</v>
+        <v>394738</v>
       </c>
       <c r="R31" t="n">
-        <v>7062309</v>
+        <v>7062311</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481492</v>
+        <v>122481482</v>
       </c>
       <c r="B32" t="n">
-        <v>79773</v>
+        <v>78741</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4302,25 +4302,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394589</v>
+        <v>394669</v>
       </c>
       <c r="R32" t="n">
-        <v>7061895</v>
+        <v>7062253</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4379,17 +4379,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122481494</v>
+        <v>122481493</v>
       </c>
       <c r="B33" t="n">
-        <v>77593</v>
+        <v>78741</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4423,21 +4423,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394802</v>
+        <v>394812</v>
       </c>
       <c r="R33" t="n">
-        <v>7062015</v>
+        <v>7062006</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481491</v>
+        <v>122483537</v>
       </c>
       <c r="B34" t="n">
-        <v>90851</v>
+        <v>78741</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4564,13 +4564,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394563</v>
+        <v>394745</v>
       </c>
       <c r="R34" t="n">
-        <v>7061882</v>
+        <v>7062367</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4629,22 +4629,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122483511</v>
+        <v>122483533</v>
       </c>
       <c r="B35" t="n">
-        <v>78740</v>
+        <v>78820</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4653,25 +4653,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394793</v>
+        <v>394737</v>
       </c>
       <c r="R35" t="n">
-        <v>7062355</v>
+        <v>7062329</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4761,7 +4761,7 @@
         <v>122483529</v>
       </c>
       <c r="B36" t="n">
-        <v>78819</v>
+        <v>78820</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483516</v>
+        <v>122483518</v>
       </c>
       <c r="B37" t="n">
-        <v>79773</v>
+        <v>78820</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4887,25 +4887,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394830</v>
+        <v>394636</v>
       </c>
       <c r="R37" t="n">
-        <v>7062019</v>
+        <v>7061901</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4959,23 +4959,22 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4993,10 +4992,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483519</v>
+        <v>122481495</v>
       </c>
       <c r="B38" t="n">
-        <v>74757</v>
+        <v>78657</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5009,21 +5008,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5033,13 +5032,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394595</v>
+        <v>394826</v>
       </c>
       <c r="R38" t="n">
-        <v>7061889</v>
+        <v>7062076</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5098,22 +5097,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122483518</v>
+        <v>122481464</v>
       </c>
       <c r="B39" t="n">
-        <v>78819</v>
+        <v>78741</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5122,25 +5121,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5150,13 +5149,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394636</v>
+        <v>394733</v>
       </c>
       <c r="R39" t="n">
-        <v>7061901</v>
+        <v>7062344</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5209,28 +5208,28 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122483537</v>
+        <v>122481491</v>
       </c>
       <c r="B40" t="n">
-        <v>78740</v>
+        <v>90852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5243,21 +5242,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5267,13 +5266,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394745</v>
+        <v>394563</v>
       </c>
       <c r="R40" t="n">
-        <v>7062367</v>
+        <v>7061882</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5332,12 +5331,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5347,7 +5346,7 @@
         <v>122483534</v>
       </c>
       <c r="B41" t="n">
-        <v>77592</v>
+        <v>77593</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5462,10 +5461,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122483532</v>
+        <v>122481466</v>
       </c>
       <c r="B42" t="n">
-        <v>82443</v>
+        <v>74758</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5478,21 +5477,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5502,13 +5501,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394743</v>
+        <v>394746</v>
       </c>
       <c r="R42" t="n">
-        <v>7062322</v>
+        <v>7062338</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5561,28 +5560,28 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481495</v>
+        <v>122481483</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5595,34 +5594,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394826</v>
+        <v>394537</v>
       </c>
       <c r="R43" t="n">
-        <v>7062076</v>
+        <v>7061922</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,6 +5661,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5665,21 +5674,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5696,10 +5690,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481482</v>
+        <v>122481473</v>
       </c>
       <c r="B44" t="n">
-        <v>78740</v>
+        <v>78741</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5736,10 +5730,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394669</v>
+        <v>394712</v>
       </c>
       <c r="R44" t="n">
-        <v>7062253</v>
+        <v>7062279</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5813,10 +5807,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122481483</v>
+        <v>122481496</v>
       </c>
       <c r="B45" t="n">
-        <v>57383</v>
+        <v>78820</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5825,43 +5819,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394537</v>
+        <v>394790</v>
       </c>
       <c r="R45" t="n">
-        <v>7061922</v>
+        <v>7062334</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5896,11 +5885,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5909,6 +5893,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>på granar gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5925,10 +5924,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122481479</v>
+        <v>122483516</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>79774</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5937,25 +5936,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5965,13 +5964,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394730</v>
+        <v>394830</v>
       </c>
       <c r="R46" t="n">
-        <v>7062309</v>
+        <v>7062019</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6009,43 +6008,44 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122481493</v>
+        <v>122481494</v>
       </c>
       <c r="B47" t="n">
-        <v>78740</v>
+        <v>77594</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6058,21 +6058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394812</v>
+        <v>394802</v>
       </c>
       <c r="R47" t="n">
-        <v>7062006</v>
+        <v>7062015</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122483535</v>
+        <v>122483514</v>
       </c>
       <c r="B48" t="n">
-        <v>78740</v>
+        <v>74763</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>283</v>
+        <v>1467</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394742</v>
+        <v>394834</v>
       </c>
       <c r="R48" t="n">
-        <v>7062337</v>
+        <v>7062076</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -4758,10 +4758,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122483529</v>
+        <v>122481495</v>
       </c>
       <c r="B36" t="n">
-        <v>78820</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4770,25 +4770,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394652</v>
+        <v>394826</v>
       </c>
       <c r="R36" t="n">
-        <v>7062221</v>
+        <v>7062076</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4863,19 +4863,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483518</v>
+        <v>122483529</v>
       </c>
       <c r="B37" t="n">
         <v>78820</v>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394636</v>
+        <v>394652</v>
       </c>
       <c r="R37" t="n">
-        <v>7061901</v>
+        <v>7062221</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4992,10 +4992,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481495</v>
+        <v>122483518</v>
       </c>
       <c r="B38" t="n">
-        <v>78657</v>
+        <v>78820</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5004,25 +5004,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394826</v>
+        <v>394636</v>
       </c>
       <c r="R38" t="n">
-        <v>7062076</v>
+        <v>7061901</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5097,12 +5097,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122483536</v>
+        <v>122483533</v>
       </c>
       <c r="B17" t="n">
-        <v>78820</v>
+        <v>78823</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394745</v>
+        <v>394737</v>
       </c>
       <c r="R17" t="n">
-        <v>7062367</v>
+        <v>7062329</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2640,17 +2640,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122481492</v>
+        <v>122481464</v>
       </c>
       <c r="B18" t="n">
-        <v>79774</v>
+        <v>78744</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,25 +2680,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394589</v>
+        <v>394733</v>
       </c>
       <c r="R18" t="n">
-        <v>7061895</v>
+        <v>7062344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2757,17 +2757,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122481479</v>
+        <v>122483536</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>78823</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394730</v>
+        <v>394745</v>
       </c>
       <c r="R19" t="n">
-        <v>7062309</v>
+        <v>7062367</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2874,38 +2874,38 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122481486</v>
+        <v>122483517</v>
       </c>
       <c r="B20" t="n">
-        <v>79739</v>
+        <v>74573</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2914,25 +2914,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6428</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394648</v>
+        <v>394786</v>
       </c>
       <c r="R20" t="n">
-        <v>7062211</v>
+        <v>7061968</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3001,28 +3001,28 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122483532</v>
+        <v>122481491</v>
       </c>
       <c r="B21" t="n">
-        <v>82444</v>
+        <v>90855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394743</v>
+        <v>394563</v>
       </c>
       <c r="R21" t="n">
-        <v>7062322</v>
+        <v>7061882</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3124,22 +3124,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122483521</v>
+        <v>122481493</v>
       </c>
       <c r="B22" t="n">
-        <v>94745</v>
+        <v>78744</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3148,25 +3148,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2668</v>
+        <v>283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394553</v>
+        <v>394812</v>
       </c>
       <c r="R22" t="n">
-        <v>7061889</v>
+        <v>7062006</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3223,30 +3223,40 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122483519</v>
+        <v>122481473</v>
       </c>
       <c r="B23" t="n">
-        <v>74758</v>
+        <v>78744</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3259,21 +3269,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3283,13 +3293,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394595</v>
+        <v>394712</v>
       </c>
       <c r="R23" t="n">
-        <v>7061889</v>
+        <v>7062279</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3342,28 +3352,28 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122483535</v>
+        <v>122483519</v>
       </c>
       <c r="B24" t="n">
-        <v>78741</v>
+        <v>74761</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3376,21 +3386,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3400,10 +3410,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394742</v>
+        <v>394595</v>
       </c>
       <c r="R24" t="n">
-        <v>7062337</v>
+        <v>7061889</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3477,10 +3487,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122483517</v>
+        <v>122483532</v>
       </c>
       <c r="B25" t="n">
-        <v>74570</v>
+        <v>82447</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3489,25 +3499,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6428</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3517,10 +3527,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394786</v>
+        <v>394743</v>
       </c>
       <c r="R25" t="n">
-        <v>7061968</v>
+        <v>7062322</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3594,10 +3604,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481467</v>
+        <v>122483518</v>
       </c>
       <c r="B26" t="n">
-        <v>77594</v>
+        <v>78823</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3606,25 +3616,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3634,13 +3644,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394746</v>
+        <v>394636</v>
       </c>
       <c r="R26" t="n">
-        <v>7062338</v>
+        <v>7061901</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3693,28 +3703,28 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122483523</v>
+        <v>122481467</v>
       </c>
       <c r="B27" t="n">
-        <v>74753</v>
+        <v>77597</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3727,21 +3737,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>310</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3751,13 +3761,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394544</v>
+        <v>394746</v>
       </c>
       <c r="R27" t="n">
-        <v>7061898</v>
+        <v>7062338</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3795,7 +3805,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3811,28 +3820,28 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122483511</v>
+        <v>122483521</v>
       </c>
       <c r="B28" t="n">
-        <v>78741</v>
+        <v>94748</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3841,25 +3850,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>2668</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3869,10 +3878,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394793</v>
+        <v>394553</v>
       </c>
       <c r="R28" t="n">
-        <v>7062355</v>
+        <v>7061889</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3916,19 +3925,9 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3946,10 +3945,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122481477</v>
+        <v>122483529</v>
       </c>
       <c r="B29" t="n">
-        <v>78820</v>
+        <v>78823</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3986,13 +3985,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394730</v>
+        <v>394652</v>
       </c>
       <c r="R29" t="n">
-        <v>7062309</v>
+        <v>7062221</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4045,28 +4044,28 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481474</v>
+        <v>122483514</v>
       </c>
       <c r="B30" t="n">
-        <v>57537</v>
+        <v>74766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4079,45 +4078,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394742</v>
+        <v>394834</v>
       </c>
       <c r="R30" t="n">
-        <v>7062294</v>
+        <v>7062076</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4157,26 +4148,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481475</v>
+        <v>122481492</v>
       </c>
       <c r="B31" t="n">
-        <v>78913</v>
+        <v>79777</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4189,21 +4195,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6459</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4213,10 +4219,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394738</v>
+        <v>394589</v>
       </c>
       <c r="R31" t="n">
-        <v>7062311</v>
+        <v>7061895</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4262,17 +4268,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4290,10 +4296,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481482</v>
+        <v>122481479</v>
       </c>
       <c r="B32" t="n">
-        <v>78741</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4306,21 +4312,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4330,10 +4336,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394669</v>
+        <v>394730</v>
       </c>
       <c r="R32" t="n">
-        <v>7062253</v>
+        <v>7062309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4389,7 +4395,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4407,10 +4413,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122481493</v>
+        <v>122483523</v>
       </c>
       <c r="B33" t="n">
-        <v>78741</v>
+        <v>74756</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4423,21 +4429,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4447,13 +4453,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394812</v>
+        <v>394544</v>
       </c>
       <c r="R33" t="n">
-        <v>7062006</v>
+        <v>7061898</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4491,6 +4497,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4506,28 +4513,28 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122483537</v>
+        <v>122481496</v>
       </c>
       <c r="B34" t="n">
-        <v>78741</v>
+        <v>78823</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4536,25 +4543,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4564,13 +4571,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394745</v>
+        <v>394790</v>
       </c>
       <c r="R34" t="n">
-        <v>7062367</v>
+        <v>7062334</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4623,28 +4630,28 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122483533</v>
+        <v>122483535</v>
       </c>
       <c r="B35" t="n">
-        <v>78820</v>
+        <v>78744</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4653,25 +4660,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4681,10 +4688,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394737</v>
+        <v>394742</v>
       </c>
       <c r="R35" t="n">
-        <v>7062329</v>
+        <v>7062337</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4758,10 +4765,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122481495</v>
+        <v>122481482</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>78744</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4774,21 +4781,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4798,10 +4805,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394826</v>
+        <v>394669</v>
       </c>
       <c r="R36" t="n">
-        <v>7062076</v>
+        <v>7062253</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4857,7 +4864,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4875,10 +4882,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483529</v>
+        <v>122483511</v>
       </c>
       <c r="B37" t="n">
-        <v>78820</v>
+        <v>78744</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4887,25 +4894,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4915,10 +4922,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394652</v>
+        <v>394793</v>
       </c>
       <c r="R37" t="n">
-        <v>7062221</v>
+        <v>7062355</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4992,10 +4999,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483518</v>
+        <v>122481475</v>
       </c>
       <c r="B38" t="n">
-        <v>78820</v>
+        <v>78916</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5004,25 +5011,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1249</v>
+        <v>6459</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5032,13 +5039,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394636</v>
+        <v>394738</v>
       </c>
       <c r="R38" t="n">
-        <v>7061901</v>
+        <v>7062311</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5097,22 +5104,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481464</v>
+        <v>122481474</v>
       </c>
       <c r="B39" t="n">
-        <v>78741</v>
+        <v>57537</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5125,34 +5132,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>283</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394733</v>
+        <v>394742</v>
       </c>
       <c r="R39" t="n">
-        <v>7062344</v>
+        <v>7062294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5195,21 +5210,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>kvistar på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5226,10 +5226,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122481491</v>
+        <v>122481486</v>
       </c>
       <c r="B40" t="n">
-        <v>90852</v>
+        <v>79742</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394563</v>
+        <v>394648</v>
       </c>
       <c r="R40" t="n">
-        <v>7061882</v>
+        <v>7062211</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122483534</v>
+        <v>122481483</v>
       </c>
       <c r="B41" t="n">
-        <v>77593</v>
+        <v>57384</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5355,41 +5355,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6000248</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394734</v>
+        <v>394537</v>
       </c>
       <c r="R41" t="n">
-        <v>7062334</v>
+        <v>7061922</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5421,50 +5426,39 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481466</v>
+        <v>122483534</v>
       </c>
       <c r="B42" t="n">
-        <v>74758</v>
+        <v>77596</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5473,25 +5467,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6000248</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5501,13 +5495,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394746</v>
+        <v>394734</v>
       </c>
       <c r="R42" t="n">
-        <v>7062338</v>
+        <v>7062334</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5545,6 +5539,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5560,28 +5555,28 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481483</v>
+        <v>122481466</v>
       </c>
       <c r="B43" t="n">
-        <v>57384</v>
+        <v>74761</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5594,39 +5589,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394537</v>
+        <v>394746</v>
       </c>
       <c r="R43" t="n">
-        <v>7061922</v>
+        <v>7062338</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5661,11 +5651,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5674,6 +5659,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>bark på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481473</v>
+        <v>122481495</v>
       </c>
       <c r="B44" t="n">
-        <v>78741</v>
+        <v>78660</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5706,21 +5706,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394712</v>
+        <v>394826</v>
       </c>
       <c r="R44" t="n">
-        <v>7062279</v>
+        <v>7062076</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5807,10 +5807,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122481496</v>
+        <v>122483516</v>
       </c>
       <c r="B45" t="n">
-        <v>78820</v>
+        <v>79777</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5819,25 +5819,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1249</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5847,13 +5847,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394790</v>
+        <v>394830</v>
       </c>
       <c r="R45" t="n">
-        <v>7062334</v>
+        <v>7062019</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5891,43 +5891,44 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122483516</v>
+        <v>122481477</v>
       </c>
       <c r="B46" t="n">
-        <v>79774</v>
+        <v>78823</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5936,25 +5937,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5964,13 +5965,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394830</v>
+        <v>394730</v>
       </c>
       <c r="R46" t="n">
-        <v>7062019</v>
+        <v>7062309</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6008,44 +6009,43 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122481494</v>
+        <v>122483537</v>
       </c>
       <c r="B47" t="n">
-        <v>77594</v>
+        <v>78744</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6058,21 +6058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394802</v>
+        <v>394745</v>
       </c>
       <c r="R47" t="n">
-        <v>7062015</v>
+        <v>7062367</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6141,28 +6141,28 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122483514</v>
+        <v>122481494</v>
       </c>
       <c r="B48" t="n">
-        <v>74763</v>
+        <v>77597</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1467</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,13 +6199,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394834</v>
+        <v>394802</v>
       </c>
       <c r="R48" t="n">
-        <v>7062076</v>
+        <v>7062015</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6258,18 +6258,18 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122483533</v>
+        <v>122481466</v>
       </c>
       <c r="B17" t="n">
-        <v>78823</v>
+        <v>74761</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394737</v>
+        <v>394746</v>
       </c>
       <c r="R17" t="n">
-        <v>7062329</v>
+        <v>7062338</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122481464</v>
+        <v>122483537</v>
       </c>
       <c r="B18" t="n">
         <v>78744</v>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394733</v>
+        <v>394745</v>
       </c>
       <c r="R18" t="n">
-        <v>7062344</v>
+        <v>7062367</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,28 +2767,28 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122483536</v>
+        <v>122483519</v>
       </c>
       <c r="B19" t="n">
-        <v>78823</v>
+        <v>74761</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394745</v>
+        <v>394595</v>
       </c>
       <c r="R19" t="n">
-        <v>7062367</v>
+        <v>7061889</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2874,17 +2874,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122481493</v>
+        <v>122481473</v>
       </c>
       <c r="B22" t="n">
         <v>78744</v>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394812</v>
+        <v>394712</v>
       </c>
       <c r="R22" t="n">
-        <v>7062006</v>
+        <v>7062279</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122481473</v>
+        <v>122481494</v>
       </c>
       <c r="B23" t="n">
-        <v>78744</v>
+        <v>77597</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3269,21 +3269,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394712</v>
+        <v>394802</v>
       </c>
       <c r="R23" t="n">
-        <v>7062279</v>
+        <v>7062015</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122483519</v>
+        <v>122483523</v>
       </c>
       <c r="B24" t="n">
-        <v>74761</v>
+        <v>74756</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394595</v>
+        <v>394544</v>
       </c>
       <c r="R24" t="n">
-        <v>7061889</v>
+        <v>7061898</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3454,6 +3454,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3487,10 +3488,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122483532</v>
+        <v>122483511</v>
       </c>
       <c r="B25" t="n">
-        <v>82447</v>
+        <v>78744</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3503,21 +3504,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3527,10 +3528,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394743</v>
+        <v>394793</v>
       </c>
       <c r="R25" t="n">
-        <v>7062322</v>
+        <v>7062355</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3604,10 +3605,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122483518</v>
+        <v>122481464</v>
       </c>
       <c r="B26" t="n">
-        <v>78823</v>
+        <v>78744</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3616,25 +3617,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3644,13 +3645,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394636</v>
+        <v>394733</v>
       </c>
       <c r="R26" t="n">
-        <v>7061901</v>
+        <v>7062344</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3703,28 +3704,28 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122481467</v>
+        <v>122481474</v>
       </c>
       <c r="B27" t="n">
-        <v>77597</v>
+        <v>57537</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3737,34 +3738,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394746</v>
+        <v>394742</v>
       </c>
       <c r="R27" t="n">
-        <v>7062338</v>
+        <v>7062294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3807,21 +3816,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>bark på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3838,10 +3832,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122483521</v>
+        <v>122481492</v>
       </c>
       <c r="B28" t="n">
-        <v>94748</v>
+        <v>79777</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3854,21 +3848,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2668</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3878,13 +3872,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394553</v>
+        <v>394589</v>
       </c>
       <c r="R28" t="n">
-        <v>7061889</v>
+        <v>7061895</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3925,30 +3919,40 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122483529</v>
+        <v>122483516</v>
       </c>
       <c r="B29" t="n">
-        <v>78823</v>
+        <v>79777</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3957,25 +3961,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1249</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3985,10 +3989,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394652</v>
+        <v>394830</v>
       </c>
       <c r="R29" t="n">
-        <v>7062221</v>
+        <v>7062019</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -4029,22 +4033,23 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4062,10 +4067,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483514</v>
+        <v>122481495</v>
       </c>
       <c r="B30" t="n">
-        <v>74766</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4078,21 +4083,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4102,13 +4107,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394834</v>
+        <v>394826</v>
       </c>
       <c r="R30" t="n">
         <v>7062076</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4167,22 +4172,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481492</v>
+        <v>122481479</v>
       </c>
       <c r="B31" t="n">
-        <v>79777</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4191,25 +4196,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4219,10 +4224,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394589</v>
+        <v>394730</v>
       </c>
       <c r="R31" t="n">
-        <v>7061895</v>
+        <v>7062309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4268,17 +4273,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4296,10 +4301,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481479</v>
+        <v>122481477</v>
       </c>
       <c r="B32" t="n">
-        <v>78660</v>
+        <v>78823</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4308,25 +4313,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4395,7 +4400,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4413,10 +4418,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483523</v>
+        <v>122483521</v>
       </c>
       <c r="B33" t="n">
-        <v>74756</v>
+        <v>94748</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4425,25 +4430,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>310</v>
+        <v>2668</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4453,10 +4458,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394544</v>
+        <v>394553</v>
       </c>
       <c r="R33" t="n">
-        <v>7061898</v>
+        <v>7061889</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4497,23 +4502,12 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4531,10 +4525,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481496</v>
+        <v>122483514</v>
       </c>
       <c r="B34" t="n">
-        <v>78823</v>
+        <v>74766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4543,25 +4537,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1249</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4571,13 +4565,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394790</v>
+        <v>394834</v>
       </c>
       <c r="R34" t="n">
-        <v>7062334</v>
+        <v>7062076</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4630,28 +4624,28 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122483535</v>
+        <v>122481483</v>
       </c>
       <c r="B35" t="n">
-        <v>78744</v>
+        <v>57384</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4664,37 +4658,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394742</v>
+        <v>394537</v>
       </c>
       <c r="R35" t="n">
-        <v>7062337</v>
+        <v>7061922</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4726,6 +4725,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4734,41 +4738,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122481482</v>
+        <v>122483518</v>
       </c>
       <c r="B36" t="n">
-        <v>78744</v>
+        <v>78823</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4777,25 +4766,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4805,13 +4794,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394669</v>
+        <v>394636</v>
       </c>
       <c r="R36" t="n">
-        <v>7062253</v>
+        <v>7061901</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4864,28 +4853,28 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483511</v>
+        <v>122483534</v>
       </c>
       <c r="B37" t="n">
-        <v>78744</v>
+        <v>77596</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4894,25 +4883,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>283</v>
+        <v>6000248</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4922,10 +4911,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394793</v>
+        <v>394734</v>
       </c>
       <c r="R37" t="n">
-        <v>7062355</v>
+        <v>7062334</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4966,6 +4955,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4999,10 +4989,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481475</v>
+        <v>122481467</v>
       </c>
       <c r="B38" t="n">
-        <v>78916</v>
+        <v>77597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5011,25 +5001,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6459</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5039,10 +5029,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394738</v>
+        <v>394746</v>
       </c>
       <c r="R38" t="n">
-        <v>7062311</v>
+        <v>7062338</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5098,7 +5088,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5116,10 +5106,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481474</v>
+        <v>122481486</v>
       </c>
       <c r="B39" t="n">
-        <v>57537</v>
+        <v>79742</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5132,42 +5122,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394742</v>
+        <v>394648</v>
       </c>
       <c r="R39" t="n">
-        <v>7062294</v>
+        <v>7062211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5210,6 +5192,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>grankvistar # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5226,10 +5223,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122481486</v>
+        <v>122483535</v>
       </c>
       <c r="B40" t="n">
-        <v>79742</v>
+        <v>78744</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5242,21 +5239,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5266,13 +5263,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394648</v>
+        <v>394742</v>
       </c>
       <c r="R40" t="n">
-        <v>7062211</v>
+        <v>7062337</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5325,28 +5322,28 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122481483</v>
+        <v>122483536</v>
       </c>
       <c r="B41" t="n">
-        <v>57384</v>
+        <v>78823</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5355,46 +5352,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394537</v>
+        <v>394745</v>
       </c>
       <c r="R41" t="n">
-        <v>7061922</v>
+        <v>7062367</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5426,11 +5418,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5439,26 +5426,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122483534</v>
+        <v>122483533</v>
       </c>
       <c r="B42" t="n">
-        <v>77596</v>
+        <v>78823</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5467,25 +5469,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6000248</v>
+        <v>1249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5495,10 +5497,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394734</v>
+        <v>394737</v>
       </c>
       <c r="R42" t="n">
-        <v>7062334</v>
+        <v>7062329</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5539,7 +5541,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5573,10 +5574,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481466</v>
+        <v>122481482</v>
       </c>
       <c r="B43" t="n">
-        <v>74761</v>
+        <v>78744</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5589,21 +5590,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5613,10 +5614,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394746</v>
+        <v>394669</v>
       </c>
       <c r="R43" t="n">
-        <v>7062338</v>
+        <v>7062253</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5672,7 +5673,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5690,10 +5691,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481495</v>
+        <v>122481493</v>
       </c>
       <c r="B44" t="n">
-        <v>78660</v>
+        <v>78744</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5706,21 +5707,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5730,10 +5731,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394826</v>
+        <v>394812</v>
       </c>
       <c r="R44" t="n">
-        <v>7062076</v>
+        <v>7062006</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5789,7 +5790,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5807,10 +5808,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122483516</v>
+        <v>122483532</v>
       </c>
       <c r="B45" t="n">
-        <v>79777</v>
+        <v>82447</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5819,25 +5820,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5847,10 +5848,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394830</v>
+        <v>394743</v>
       </c>
       <c r="R45" t="n">
-        <v>7062019</v>
+        <v>7062322</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5891,23 +5892,22 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5925,7 +5925,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122481477</v>
+        <v>122481496</v>
       </c>
       <c r="B46" t="n">
         <v>78823</v>
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394730</v>
+        <v>394790</v>
       </c>
       <c r="R46" t="n">
-        <v>7062309</v>
+        <v>7062334</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6042,10 +6042,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122483537</v>
+        <v>122483529</v>
       </c>
       <c r="B47" t="n">
-        <v>78744</v>
+        <v>78823</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6054,25 +6054,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394745</v>
+        <v>394652</v>
       </c>
       <c r="R47" t="n">
-        <v>7062367</v>
+        <v>7062221</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122481494</v>
+        <v>122481475</v>
       </c>
       <c r="B48" t="n">
-        <v>77597</v>
+        <v>78916</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6171,25 +6171,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>6459</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394802</v>
+        <v>394738</v>
       </c>
       <c r="R48" t="n">
-        <v>7062015</v>
+        <v>7062311</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -4067,10 +4067,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481495</v>
+        <v>122481477</v>
       </c>
       <c r="B30" t="n">
-        <v>78660</v>
+        <v>78823</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394826</v>
+        <v>394730</v>
       </c>
       <c r="R30" t="n">
-        <v>7062076</v>
+        <v>7062309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481479</v>
+        <v>122483521</v>
       </c>
       <c r="B31" t="n">
-        <v>78660</v>
+        <v>94748</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4196,25 +4196,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2668</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4224,13 +4224,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394730</v>
+        <v>394553</v>
       </c>
       <c r="R31" t="n">
-        <v>7062309</v>
+        <v>7061889</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4271,40 +4271,30 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481477</v>
+        <v>122481495</v>
       </c>
       <c r="B32" t="n">
-        <v>78823</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4313,25 +4303,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4341,10 +4331,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394730</v>
+        <v>394826</v>
       </c>
       <c r="R32" t="n">
-        <v>7062309</v>
+        <v>7062076</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4400,7 +4390,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4418,10 +4408,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483521</v>
+        <v>122481479</v>
       </c>
       <c r="B33" t="n">
-        <v>94748</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4430,25 +4420,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2668</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4458,13 +4448,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394553</v>
+        <v>394730</v>
       </c>
       <c r="R33" t="n">
-        <v>7061889</v>
+        <v>7062309</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4505,20 +4495,30 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481467</v>
+        <v>122481486</v>
       </c>
       <c r="B38" t="n">
-        <v>77597</v>
+        <v>79742</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394746</v>
+        <v>394648</v>
       </c>
       <c r="R38" t="n">
-        <v>7062338</v>
+        <v>7062211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481486</v>
+        <v>122481467</v>
       </c>
       <c r="B39" t="n">
-        <v>79742</v>
+        <v>77597</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5122,21 +5122,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394648</v>
+        <v>394746</v>
       </c>
       <c r="R39" t="n">
-        <v>7062211</v>
+        <v>7062338</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -4989,10 +4989,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481486</v>
+        <v>122481467</v>
       </c>
       <c r="B38" t="n">
-        <v>79742</v>
+        <v>77597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394648</v>
+        <v>394746</v>
       </c>
       <c r="R38" t="n">
-        <v>7062211</v>
+        <v>7062338</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481467</v>
+        <v>122481486</v>
       </c>
       <c r="B39" t="n">
-        <v>77597</v>
+        <v>79742</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5122,21 +5122,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394746</v>
+        <v>394648</v>
       </c>
       <c r="R39" t="n">
-        <v>7062338</v>
+        <v>7062211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -4067,10 +4067,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481477</v>
+        <v>122481495</v>
       </c>
       <c r="B30" t="n">
-        <v>78823</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394730</v>
+        <v>394826</v>
       </c>
       <c r="R30" t="n">
-        <v>7062309</v>
+        <v>7062076</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122483521</v>
+        <v>122481479</v>
       </c>
       <c r="B31" t="n">
-        <v>94748</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4196,25 +4196,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2668</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4224,13 +4224,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394553</v>
+        <v>394730</v>
       </c>
       <c r="R31" t="n">
-        <v>7061889</v>
+        <v>7062309</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4271,30 +4271,40 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481495</v>
+        <v>122481477</v>
       </c>
       <c r="B32" t="n">
-        <v>78660</v>
+        <v>78823</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4303,25 +4313,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4331,10 +4341,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394826</v>
+        <v>394730</v>
       </c>
       <c r="R32" t="n">
-        <v>7062076</v>
+        <v>7062309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4390,7 +4400,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4408,10 +4418,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122481479</v>
+        <v>122483521</v>
       </c>
       <c r="B33" t="n">
-        <v>78660</v>
+        <v>94748</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4420,25 +4430,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2668</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4448,13 +4458,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394730</v>
+        <v>394553</v>
       </c>
       <c r="R33" t="n">
-        <v>7062309</v>
+        <v>7061889</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,30 +4505,20 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481467</v>
+        <v>122481486</v>
       </c>
       <c r="B38" t="n">
-        <v>77597</v>
+        <v>79742</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394746</v>
+        <v>394648</v>
       </c>
       <c r="R38" t="n">
-        <v>7062338</v>
+        <v>7062211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481486</v>
+        <v>122481467</v>
       </c>
       <c r="B39" t="n">
-        <v>79742</v>
+        <v>77597</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5122,21 +5122,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394648</v>
+        <v>394746</v>
       </c>
       <c r="R39" t="n">
-        <v>7062211</v>
+        <v>7062338</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122481466</v>
+        <v>122483537</v>
       </c>
       <c r="B17" t="n">
-        <v>74761</v>
+        <v>78744</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394746</v>
+        <v>394745</v>
       </c>
       <c r="R17" t="n">
-        <v>7062338</v>
+        <v>7062367</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,28 +2650,28 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122483537</v>
+        <v>122481466</v>
       </c>
       <c r="B18" t="n">
-        <v>78744</v>
+        <v>74761</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394745</v>
+        <v>394746</v>
       </c>
       <c r="R18" t="n">
-        <v>7062367</v>
+        <v>7062338</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,18 +2767,18 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481495</v>
+        <v>122481477</v>
       </c>
       <c r="B30" t="n">
-        <v>78660</v>
+        <v>78823</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394826</v>
+        <v>394730</v>
       </c>
       <c r="R30" t="n">
-        <v>7062076</v>
+        <v>7062309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481479</v>
+        <v>122483521</v>
       </c>
       <c r="B31" t="n">
-        <v>78660</v>
+        <v>94748</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4196,25 +4196,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2668</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4224,13 +4224,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394730</v>
+        <v>394553</v>
       </c>
       <c r="R31" t="n">
-        <v>7062309</v>
+        <v>7061889</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4271,40 +4271,30 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481477</v>
+        <v>122481495</v>
       </c>
       <c r="B32" t="n">
-        <v>78823</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4313,25 +4303,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4341,10 +4331,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394730</v>
+        <v>394826</v>
       </c>
       <c r="R32" t="n">
-        <v>7062309</v>
+        <v>7062076</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4400,7 +4390,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4418,10 +4408,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483521</v>
+        <v>122481479</v>
       </c>
       <c r="B33" t="n">
-        <v>94748</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4430,25 +4420,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2668</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4458,13 +4448,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394553</v>
+        <v>394730</v>
       </c>
       <c r="R33" t="n">
-        <v>7061889</v>
+        <v>7062309</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4505,20 +4495,30 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -4067,10 +4067,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481477</v>
+        <v>122481495</v>
       </c>
       <c r="B30" t="n">
-        <v>78823</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394730</v>
+        <v>394826</v>
       </c>
       <c r="R30" t="n">
-        <v>7062309</v>
+        <v>7062076</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122483521</v>
+        <v>122481479</v>
       </c>
       <c r="B31" t="n">
-        <v>94748</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4196,25 +4196,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2668</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4224,13 +4224,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394553</v>
+        <v>394730</v>
       </c>
       <c r="R31" t="n">
-        <v>7061889</v>
+        <v>7062309</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4271,30 +4271,40 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481495</v>
+        <v>122481477</v>
       </c>
       <c r="B32" t="n">
-        <v>78660</v>
+        <v>78823</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4303,25 +4313,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4331,10 +4341,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394826</v>
+        <v>394730</v>
       </c>
       <c r="R32" t="n">
-        <v>7062076</v>
+        <v>7062309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4390,7 +4400,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4408,10 +4418,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122481479</v>
+        <v>122483521</v>
       </c>
       <c r="B33" t="n">
-        <v>78660</v>
+        <v>94748</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4420,25 +4430,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2668</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4448,13 +4458,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394730</v>
+        <v>394553</v>
       </c>
       <c r="R33" t="n">
-        <v>7062309</v>
+        <v>7061889</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,30 +4505,20 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122483537</v>
+        <v>122481464</v>
       </c>
       <c r="B17" t="n">
-        <v>78744</v>
+        <v>78846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394745</v>
+        <v>394733</v>
       </c>
       <c r="R17" t="n">
-        <v>7062367</v>
+        <v>7062344</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,28 +2650,28 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122481466</v>
+        <v>122481496</v>
       </c>
       <c r="B18" t="n">
-        <v>74761</v>
+        <v>78925</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,25 +2680,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394746</v>
+        <v>394790</v>
       </c>
       <c r="R18" t="n">
-        <v>7062338</v>
+        <v>7062334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122483519</v>
+        <v>122481483</v>
       </c>
       <c r="B19" t="n">
-        <v>74761</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,37 +2801,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394595</v>
+        <v>394537</v>
       </c>
       <c r="R19" t="n">
-        <v>7061889</v>
+        <v>7061922</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2863,6 +2868,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2871,41 +2881,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122483517</v>
+        <v>122481467</v>
       </c>
       <c r="B20" t="n">
-        <v>74573</v>
+        <v>77699</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2914,25 +2909,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2942,13 +2937,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394786</v>
+        <v>394746</v>
       </c>
       <c r="R20" t="n">
-        <v>7061968</v>
+        <v>7062338</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3001,28 +2996,28 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122481491</v>
+        <v>122481486</v>
       </c>
       <c r="B21" t="n">
-        <v>90855</v>
+        <v>79844</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3035,21 +3030,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3059,10 +3054,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394563</v>
+        <v>394648</v>
       </c>
       <c r="R21" t="n">
-        <v>7061882</v>
+        <v>7062211</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3118,7 +3113,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3136,10 +3131,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122481473</v>
+        <v>122483536</v>
       </c>
       <c r="B22" t="n">
-        <v>78744</v>
+        <v>78925</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3148,25 +3143,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3176,13 +3171,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394712</v>
+        <v>394745</v>
       </c>
       <c r="R22" t="n">
-        <v>7062279</v>
+        <v>7062367</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3225,38 +3220,38 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122481494</v>
+        <v>122483514</v>
       </c>
       <c r="B23" t="n">
-        <v>77597</v>
+        <v>74868</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3269,21 +3264,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3293,13 +3288,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394802</v>
+        <v>394834</v>
       </c>
       <c r="R23" t="n">
-        <v>7062015</v>
+        <v>7062076</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3352,18 +3347,18 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3373,7 +3368,7 @@
         <v>122483523</v>
       </c>
       <c r="B24" t="n">
-        <v>74756</v>
+        <v>74858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3488,10 +3483,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122483511</v>
+        <v>122483535</v>
       </c>
       <c r="B25" t="n">
-        <v>78744</v>
+        <v>78846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3528,10 +3523,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394793</v>
+        <v>394742</v>
       </c>
       <c r="R25" t="n">
-        <v>7062355</v>
+        <v>7062337</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3605,10 +3600,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481464</v>
+        <v>122481473</v>
       </c>
       <c r="B26" t="n">
-        <v>78744</v>
+        <v>78846</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3645,10 +3640,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394733</v>
+        <v>394712</v>
       </c>
       <c r="R26" t="n">
-        <v>7062344</v>
+        <v>7062279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3722,10 +3717,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122481474</v>
+        <v>122481492</v>
       </c>
       <c r="B27" t="n">
-        <v>57537</v>
+        <v>79879</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3734,46 +3729,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394742</v>
+        <v>394589</v>
       </c>
       <c r="R27" t="n">
-        <v>7062294</v>
+        <v>7061895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3816,6 +3803,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3832,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122481492</v>
+        <v>122483511</v>
       </c>
       <c r="B28" t="n">
-        <v>79777</v>
+        <v>78846</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3844,25 +3846,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3872,13 +3874,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394589</v>
+        <v>394793</v>
       </c>
       <c r="R28" t="n">
-        <v>7061895</v>
+        <v>7062355</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3921,38 +3923,38 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122483516</v>
+        <v>122483529</v>
       </c>
       <c r="B29" t="n">
-        <v>79777</v>
+        <v>78925</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3961,25 +3963,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3989,10 +3991,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394830</v>
+        <v>394652</v>
       </c>
       <c r="R29" t="n">
-        <v>7062019</v>
+        <v>7062221</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -4033,23 +4035,22 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4067,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481495</v>
+        <v>122483519</v>
       </c>
       <c r="B30" t="n">
-        <v>78660</v>
+        <v>74863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4083,21 +4084,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4107,13 +4108,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394826</v>
+        <v>394595</v>
       </c>
       <c r="R30" t="n">
-        <v>7062076</v>
+        <v>7061889</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4172,22 +4173,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481479</v>
+        <v>122481474</v>
       </c>
       <c r="B31" t="n">
-        <v>78660</v>
+        <v>57631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4200,34 +4201,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394730</v>
+        <v>394742</v>
       </c>
       <c r="R31" t="n">
-        <v>7062309</v>
+        <v>7062294</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4270,21 +4279,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4301,10 +4295,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481477</v>
+        <v>122481482</v>
       </c>
       <c r="B32" t="n">
-        <v>78823</v>
+        <v>78846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4313,25 +4307,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4341,10 +4335,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394730</v>
+        <v>394669</v>
       </c>
       <c r="R32" t="n">
-        <v>7062309</v>
+        <v>7062253</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4400,7 +4394,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4418,10 +4412,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483521</v>
+        <v>122481493</v>
       </c>
       <c r="B33" t="n">
-        <v>94748</v>
+        <v>78846</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4430,25 +4424,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2668</v>
+        <v>283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4458,13 +4452,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394553</v>
+        <v>394812</v>
       </c>
       <c r="R33" t="n">
-        <v>7061889</v>
+        <v>7062006</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4505,30 +4499,40 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122483514</v>
+        <v>122483533</v>
       </c>
       <c r="B34" t="n">
-        <v>74766</v>
+        <v>78925</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4537,25 +4541,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4565,10 +4569,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394834</v>
+        <v>394737</v>
       </c>
       <c r="R34" t="n">
-        <v>7062076</v>
+        <v>7062329</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4642,10 +4646,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122481483</v>
+        <v>122481477</v>
       </c>
       <c r="B35" t="n">
-        <v>57384</v>
+        <v>78925</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4654,43 +4658,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394537</v>
+        <v>394730</v>
       </c>
       <c r="R35" t="n">
-        <v>7061922</v>
+        <v>7062309</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4725,11 +4724,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4738,6 +4732,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>grenar på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4754,10 +4763,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122483518</v>
+        <v>122483516</v>
       </c>
       <c r="B36" t="n">
-        <v>78823</v>
+        <v>79879</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4766,25 +4775,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1249</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4794,10 +4803,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394636</v>
+        <v>394830</v>
       </c>
       <c r="R36" t="n">
-        <v>7061901</v>
+        <v>7062019</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4838,22 +4847,23 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4871,10 +4881,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483534</v>
+        <v>122483518</v>
       </c>
       <c r="B37" t="n">
-        <v>77596</v>
+        <v>78925</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4883,25 +4893,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6000248</v>
+        <v>1249</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4911,10 +4921,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394734</v>
+        <v>394636</v>
       </c>
       <c r="R37" t="n">
-        <v>7062334</v>
+        <v>7061901</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4955,7 +4965,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4989,10 +4998,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481467</v>
+        <v>122483537</v>
       </c>
       <c r="B38" t="n">
-        <v>77597</v>
+        <v>78846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5005,21 +5014,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5029,13 +5038,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394746</v>
+        <v>394745</v>
       </c>
       <c r="R38" t="n">
-        <v>7062338</v>
+        <v>7062367</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5088,28 +5097,28 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481486</v>
+        <v>122481491</v>
       </c>
       <c r="B39" t="n">
-        <v>79742</v>
+        <v>90958</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5122,21 +5131,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5146,10 +5155,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394648</v>
+        <v>394563</v>
       </c>
       <c r="R39" t="n">
-        <v>7062211</v>
+        <v>7061882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5205,7 +5214,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5223,10 +5232,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122483535</v>
+        <v>122483521</v>
       </c>
       <c r="B40" t="n">
-        <v>78744</v>
+        <v>94851</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5235,25 +5244,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>283</v>
+        <v>2668</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5263,10 +5272,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394742</v>
+        <v>394553</v>
       </c>
       <c r="R40" t="n">
-        <v>7062337</v>
+        <v>7061889</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5310,19 +5319,9 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5340,10 +5339,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122483536</v>
+        <v>122481494</v>
       </c>
       <c r="B41" t="n">
-        <v>78823</v>
+        <v>77699</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5352,25 +5351,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5380,13 +5379,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394745</v>
+        <v>394802</v>
       </c>
       <c r="R41" t="n">
-        <v>7062367</v>
+        <v>7062015</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5429,38 +5428,38 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122483533</v>
+        <v>122481479</v>
       </c>
       <c r="B42" t="n">
-        <v>78823</v>
+        <v>78762</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5469,25 +5468,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5497,13 +5496,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394737</v>
+        <v>394730</v>
       </c>
       <c r="R42" t="n">
-        <v>7062329</v>
+        <v>7062309</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5562,22 +5561,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481482</v>
+        <v>122481475</v>
       </c>
       <c r="B43" t="n">
-        <v>78744</v>
+        <v>79018</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5586,25 +5585,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>283</v>
+        <v>6459</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5614,10 +5613,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394669</v>
+        <v>394738</v>
       </c>
       <c r="R43" t="n">
-        <v>7062253</v>
+        <v>7062311</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5673,7 +5672,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5691,10 +5690,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481493</v>
+        <v>122481495</v>
       </c>
       <c r="B44" t="n">
-        <v>78744</v>
+        <v>78762</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5707,21 +5706,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5731,10 +5730,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394812</v>
+        <v>394826</v>
       </c>
       <c r="R44" t="n">
-        <v>7062006</v>
+        <v>7062076</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5790,7 +5789,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5808,10 +5807,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122483532</v>
+        <v>122483534</v>
       </c>
       <c r="B45" t="n">
-        <v>82447</v>
+        <v>77698</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5820,25 +5819,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6000248</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5848,10 +5847,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394743</v>
+        <v>394734</v>
       </c>
       <c r="R45" t="n">
-        <v>7062322</v>
+        <v>7062334</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5892,6 +5891,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122481496</v>
+        <v>122483532</v>
       </c>
       <c r="B46" t="n">
-        <v>78823</v>
+        <v>82549</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5937,25 +5937,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1249</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5965,13 +5965,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394790</v>
+        <v>394743</v>
       </c>
       <c r="R46" t="n">
-        <v>7062334</v>
+        <v>7062322</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6024,28 +6024,28 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122483529</v>
+        <v>122481466</v>
       </c>
       <c r="B47" t="n">
-        <v>78823</v>
+        <v>74863</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6054,25 +6054,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394652</v>
+        <v>394746</v>
       </c>
       <c r="R47" t="n">
-        <v>7062221</v>
+        <v>7062338</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6141,28 +6141,28 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122481475</v>
+        <v>122483517</v>
       </c>
       <c r="B48" t="n">
-        <v>78916</v>
+        <v>74675</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6459</v>
+        <v>6428</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,13 +6199,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394738</v>
+        <v>394786</v>
       </c>
       <c r="R48" t="n">
-        <v>7062311</v>
+        <v>7061968</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6264,12 +6264,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2897,10 +2897,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122481467</v>
+        <v>122481486</v>
       </c>
       <c r="B20" t="n">
-        <v>77699</v>
+        <v>79844</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394746</v>
+        <v>394648</v>
       </c>
       <c r="R20" t="n">
-        <v>7062338</v>
+        <v>7062211</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122481486</v>
+        <v>122481467</v>
       </c>
       <c r="B21" t="n">
-        <v>79844</v>
+        <v>77699</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394648</v>
+        <v>394746</v>
       </c>
       <c r="R21" t="n">
-        <v>7062211</v>
+        <v>7062338</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122481494</v>
+        <v>122481479</v>
       </c>
       <c r="B41" t="n">
-        <v>77699</v>
+        <v>78762</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394802</v>
+        <v>394730</v>
       </c>
       <c r="R41" t="n">
-        <v>7062015</v>
+        <v>7062309</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481479</v>
+        <v>122481494</v>
       </c>
       <c r="B42" t="n">
-        <v>78762</v>
+        <v>77699</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5472,21 +5472,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394730</v>
+        <v>394802</v>
       </c>
       <c r="R42" t="n">
-        <v>7062309</v>
+        <v>7062015</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5690,10 +5690,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481495</v>
+        <v>122483534</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
+        <v>77698</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5702,25 +5702,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6000248</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5730,13 +5730,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394826</v>
+        <v>394734</v>
       </c>
       <c r="R44" t="n">
-        <v>7062076</v>
+        <v>7062334</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5774,6 +5774,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5795,22 +5796,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122483534</v>
+        <v>122481495</v>
       </c>
       <c r="B45" t="n">
-        <v>77698</v>
+        <v>78762</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5819,25 +5820,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6000248</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5847,13 +5848,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394734</v>
+        <v>394826</v>
       </c>
       <c r="R45" t="n">
-        <v>7062334</v>
+        <v>7062076</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5891,7 +5892,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5913,12 +5913,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -4295,10 +4295,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122481482</v>
+        <v>122483533</v>
       </c>
       <c r="B32" t="n">
-        <v>78846</v>
+        <v>78925</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4307,25 +4307,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4335,13 +4335,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394669</v>
+        <v>394737</v>
       </c>
       <c r="R32" t="n">
-        <v>7062253</v>
+        <v>7062329</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4394,28 +4394,28 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122481493</v>
+        <v>122481477</v>
       </c>
       <c r="B33" t="n">
-        <v>78846</v>
+        <v>78925</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4424,25 +4424,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394812</v>
+        <v>394730</v>
       </c>
       <c r="R33" t="n">
-        <v>7062006</v>
+        <v>7062309</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122483533</v>
+        <v>122481482</v>
       </c>
       <c r="B34" t="n">
-        <v>78925</v>
+        <v>78846</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4541,25 +4541,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4569,13 +4569,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394737</v>
+        <v>394669</v>
       </c>
       <c r="R34" t="n">
-        <v>7062329</v>
+        <v>7062253</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4628,28 +4628,28 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122481477</v>
+        <v>122481493</v>
       </c>
       <c r="B35" t="n">
-        <v>78925</v>
+        <v>78846</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4658,25 +4658,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394730</v>
+        <v>394812</v>
       </c>
       <c r="R35" t="n">
-        <v>7062309</v>
+        <v>7062006</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5115,10 +5115,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481491</v>
+        <v>122483521</v>
       </c>
       <c r="B39" t="n">
-        <v>90958</v>
+        <v>94851</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5127,25 +5127,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>2668</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5155,13 +5155,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394563</v>
+        <v>394553</v>
       </c>
       <c r="R39" t="n">
-        <v>7061882</v>
+        <v>7061889</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5202,40 +5202,30 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122483521</v>
+        <v>122481491</v>
       </c>
       <c r="B40" t="n">
-        <v>94851</v>
+        <v>90958</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5244,25 +5234,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2668</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5272,13 +5262,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394553</v>
+        <v>394563</v>
       </c>
       <c r="R40" t="n">
-        <v>7061889</v>
+        <v>7061882</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5319,30 +5309,40 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122481479</v>
+        <v>122481494</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>77699</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394730</v>
+        <v>394802</v>
       </c>
       <c r="R41" t="n">
-        <v>7062309</v>
+        <v>7062015</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481494</v>
+        <v>122481479</v>
       </c>
       <c r="B42" t="n">
-        <v>77699</v>
+        <v>78762</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5472,21 +5472,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394802</v>
+        <v>394730</v>
       </c>
       <c r="R42" t="n">
-        <v>7062015</v>
+        <v>7062309</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5690,10 +5690,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122483534</v>
+        <v>122481495</v>
       </c>
       <c r="B44" t="n">
-        <v>77698</v>
+        <v>78762</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5702,25 +5702,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6000248</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5730,13 +5730,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394734</v>
+        <v>394826</v>
       </c>
       <c r="R44" t="n">
-        <v>7062334</v>
+        <v>7062076</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5774,7 +5774,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5796,22 +5795,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122481495</v>
+        <v>122483534</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>77698</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5820,25 +5819,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6000248</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5848,13 +5847,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394826</v>
+        <v>394734</v>
       </c>
       <c r="R45" t="n">
-        <v>7062076</v>
+        <v>7062334</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5892,6 +5891,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5913,12 +5913,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122481464</v>
+        <v>122481496</v>
       </c>
       <c r="B17" t="n">
-        <v>78846</v>
+        <v>78929</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394733</v>
+        <v>394790</v>
       </c>
       <c r="R17" t="n">
-        <v>7062344</v>
+        <v>7062334</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122481496</v>
+        <v>122483521</v>
       </c>
       <c r="B18" t="n">
-        <v>78925</v>
+        <v>94859</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,25 +2680,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1249</v>
+        <v>2668</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394790</v>
+        <v>394553</v>
       </c>
       <c r="R18" t="n">
-        <v>7062334</v>
+        <v>7061889</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2755,40 +2755,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122481483</v>
+        <v>122483532</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,42 +2791,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394537</v>
+        <v>394743</v>
       </c>
       <c r="R19" t="n">
-        <v>7061922</v>
+        <v>7062322</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2868,11 +2853,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2881,26 +2861,41 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122481486</v>
+        <v>122481466</v>
       </c>
       <c r="B20" t="n">
-        <v>79844</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2913,21 +2908,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394648</v>
+        <v>394746</v>
       </c>
       <c r="R20" t="n">
-        <v>7062211</v>
+        <v>7062338</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2996,7 +2991,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3014,10 +3009,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122481467</v>
+        <v>122481479</v>
       </c>
       <c r="B21" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3030,21 +3025,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3054,10 +3049,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394746</v>
+        <v>394730</v>
       </c>
       <c r="R21" t="n">
-        <v>7062338</v>
+        <v>7062309</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3113,7 +3108,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3131,10 +3126,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122483536</v>
+        <v>122481464</v>
       </c>
       <c r="B22" t="n">
-        <v>78925</v>
+        <v>78850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3143,25 +3138,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3171,13 +3166,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394745</v>
+        <v>394733</v>
       </c>
       <c r="R22" t="n">
-        <v>7062367</v>
+        <v>7062344</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3220,38 +3215,38 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122483514</v>
+        <v>122481474</v>
       </c>
       <c r="B23" t="n">
-        <v>74868</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3264,37 +3259,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394834</v>
+        <v>394742</v>
       </c>
       <c r="R23" t="n">
-        <v>7062076</v>
+        <v>7062294</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3334,31 +3337,16 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3483,10 +3471,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122483535</v>
+        <v>122481486</v>
       </c>
       <c r="B25" t="n">
-        <v>78846</v>
+        <v>79848</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3499,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>283</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3523,13 +3511,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394742</v>
+        <v>394648</v>
       </c>
       <c r="R25" t="n">
-        <v>7062337</v>
+        <v>7062211</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3582,28 +3570,28 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481473</v>
+        <v>122481475</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>79022</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3612,25 +3600,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>283</v>
+        <v>6459</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3640,10 +3628,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394712</v>
+        <v>394738</v>
       </c>
       <c r="R26" t="n">
-        <v>7062279</v>
+        <v>7062311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3699,7 +3687,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3717,10 +3705,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122481492</v>
+        <v>122483514</v>
       </c>
       <c r="B27" t="n">
-        <v>79879</v>
+        <v>74868</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3729,25 +3717,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>1467</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3757,13 +3745,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394589</v>
+        <v>394834</v>
       </c>
       <c r="R27" t="n">
-        <v>7061895</v>
+        <v>7062076</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3806,38 +3794,38 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122483511</v>
+        <v>122481494</v>
       </c>
       <c r="B28" t="n">
-        <v>78846</v>
+        <v>77699</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3850,21 +3838,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3874,13 +3862,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394793</v>
+        <v>394802</v>
       </c>
       <c r="R28" t="n">
-        <v>7062355</v>
+        <v>7062015</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3933,28 +3921,28 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122483529</v>
+        <v>122481495</v>
       </c>
       <c r="B29" t="n">
-        <v>78925</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3963,25 +3951,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3991,13 +3979,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394652</v>
+        <v>394826</v>
       </c>
       <c r="R29" t="n">
-        <v>7062221</v>
+        <v>7062076</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4056,22 +4044,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483519</v>
+        <v>122483537</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>78850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4084,21 +4072,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4108,10 +4096,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394595</v>
+        <v>394745</v>
       </c>
       <c r="R30" t="n">
-        <v>7061889</v>
+        <v>7062367</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4185,10 +4173,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481474</v>
+        <v>122481493</v>
       </c>
       <c r="B31" t="n">
-        <v>57631</v>
+        <v>78850</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4201,42 +4189,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394742</v>
+        <v>394812</v>
       </c>
       <c r="R31" t="n">
-        <v>7062294</v>
+        <v>7062006</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4279,6 +4259,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4295,10 +4290,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122483533</v>
+        <v>122483536</v>
       </c>
       <c r="B32" t="n">
-        <v>78925</v>
+        <v>78929</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4335,10 +4330,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394737</v>
+        <v>394745</v>
       </c>
       <c r="R32" t="n">
-        <v>7062329</v>
+        <v>7062367</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4384,17 +4379,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4412,10 +4407,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122481477</v>
+        <v>122483529</v>
       </c>
       <c r="B33" t="n">
-        <v>78925</v>
+        <v>78929</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4452,13 +4447,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394730</v>
+        <v>394652</v>
       </c>
       <c r="R33" t="n">
-        <v>7062309</v>
+        <v>7062221</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4511,28 +4506,28 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481482</v>
+        <v>122483518</v>
       </c>
       <c r="B34" t="n">
-        <v>78846</v>
+        <v>78929</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4541,25 +4536,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4569,13 +4564,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394669</v>
+        <v>394636</v>
       </c>
       <c r="R34" t="n">
-        <v>7062253</v>
+        <v>7061901</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4628,28 +4623,28 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122481493</v>
+        <v>122483511</v>
       </c>
       <c r="B35" t="n">
-        <v>78846</v>
+        <v>78850</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4686,13 +4681,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394812</v>
+        <v>394793</v>
       </c>
       <c r="R35" t="n">
-        <v>7062006</v>
+        <v>7062355</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4745,28 +4740,28 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122483516</v>
+        <v>122481477</v>
       </c>
       <c r="B36" t="n">
-        <v>79879</v>
+        <v>78929</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4775,25 +4770,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4803,13 +4798,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394830</v>
+        <v>394730</v>
       </c>
       <c r="R36" t="n">
-        <v>7062019</v>
+        <v>7062309</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4847,44 +4842,43 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483518</v>
+        <v>122481482</v>
       </c>
       <c r="B37" t="n">
-        <v>78925</v>
+        <v>78850</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4893,25 +4887,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4921,13 +4915,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394636</v>
+        <v>394669</v>
       </c>
       <c r="R37" t="n">
-        <v>7061901</v>
+        <v>7062253</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4980,28 +4974,28 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483537</v>
+        <v>122483535</v>
       </c>
       <c r="B38" t="n">
-        <v>78846</v>
+        <v>78850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5038,10 +5032,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394745</v>
+        <v>394742</v>
       </c>
       <c r="R38" t="n">
-        <v>7062367</v>
+        <v>7062337</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -5115,10 +5109,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122483521</v>
+        <v>122481473</v>
       </c>
       <c r="B39" t="n">
-        <v>94851</v>
+        <v>78850</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5127,25 +5121,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2668</v>
+        <v>283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5155,13 +5149,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394553</v>
+        <v>394712</v>
       </c>
       <c r="R39" t="n">
-        <v>7061889</v>
+        <v>7062279</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5202,30 +5196,40 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122481491</v>
+        <v>122483534</v>
       </c>
       <c r="B40" t="n">
-        <v>90958</v>
+        <v>77698</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5234,25 +5238,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6000248</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5262,13 +5266,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394563</v>
+        <v>394734</v>
       </c>
       <c r="R40" t="n">
-        <v>7061882</v>
+        <v>7062334</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5306,6 +5310,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5327,22 +5332,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122481494</v>
+        <v>122481491</v>
       </c>
       <c r="B41" t="n">
-        <v>77699</v>
+        <v>90962</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5355,21 +5360,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5379,10 +5384,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394802</v>
+        <v>394563</v>
       </c>
       <c r="R41" t="n">
-        <v>7062015</v>
+        <v>7061882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5438,7 +5443,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5456,10 +5461,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481479</v>
+        <v>122483533</v>
       </c>
       <c r="B42" t="n">
-        <v>78762</v>
+        <v>78929</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5468,25 +5473,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5496,13 +5501,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394730</v>
+        <v>394737</v>
       </c>
       <c r="R42" t="n">
-        <v>7062309</v>
+        <v>7062329</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5561,22 +5566,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481475</v>
+        <v>122483516</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79883</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5589,21 +5594,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6459</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5613,13 +5618,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394738</v>
+        <v>394830</v>
       </c>
       <c r="R43" t="n">
-        <v>7062311</v>
+        <v>7062019</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5657,43 +5662,44 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481495</v>
+        <v>122483519</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5706,21 +5712,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5730,13 +5736,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394826</v>
+        <v>394595</v>
       </c>
       <c r="R44" t="n">
-        <v>7062076</v>
+        <v>7061889</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5795,22 +5801,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122483534</v>
+        <v>122481483</v>
       </c>
       <c r="B45" t="n">
-        <v>77698</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5819,41 +5825,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6000248</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394734</v>
+        <v>394537</v>
       </c>
       <c r="R45" t="n">
-        <v>7062334</v>
+        <v>7061922</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5885,50 +5896,39 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122483532</v>
+        <v>122481467</v>
       </c>
       <c r="B46" t="n">
-        <v>82549</v>
+        <v>77699</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5941,21 +5941,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5965,13 +5965,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394743</v>
+        <v>394746</v>
       </c>
       <c r="R46" t="n">
-        <v>7062322</v>
+        <v>7062338</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6024,28 +6024,28 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122481466</v>
+        <v>122483517</v>
       </c>
       <c r="B47" t="n">
-        <v>74863</v>
+        <v>74675</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6054,25 +6054,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394746</v>
+        <v>394786</v>
       </c>
       <c r="R47" t="n">
-        <v>7062338</v>
+        <v>7061968</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6141,28 +6141,28 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122483517</v>
+        <v>122481492</v>
       </c>
       <c r="B48" t="n">
-        <v>74675</v>
+        <v>79883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6428</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,13 +6199,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394786</v>
+        <v>394589</v>
       </c>
       <c r="R48" t="n">
-        <v>7061968</v>
+        <v>7061895</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6248,28 +6248,28 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122481496</v>
+        <v>122483516</v>
       </c>
       <c r="B17" t="n">
-        <v>78929</v>
+        <v>79883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1249</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394790</v>
+        <v>394830</v>
       </c>
       <c r="R17" t="n">
-        <v>7062334</v>
+        <v>7062019</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2635,43 +2635,44 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122483521</v>
+        <v>122483518</v>
       </c>
       <c r="B18" t="n">
-        <v>94859</v>
+        <v>78929</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,25 +2681,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2668</v>
+        <v>1249</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,10 +2709,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394553</v>
+        <v>394636</v>
       </c>
       <c r="R18" t="n">
-        <v>7061889</v>
+        <v>7061901</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2755,9 +2756,19 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2775,10 +2786,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122483532</v>
+        <v>122481464</v>
       </c>
       <c r="B19" t="n">
-        <v>82553</v>
+        <v>78850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2791,21 +2802,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2815,13 +2826,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394743</v>
+        <v>394733</v>
       </c>
       <c r="R19" t="n">
-        <v>7062322</v>
+        <v>7062344</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2874,28 +2885,28 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122481466</v>
+        <v>122483517</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
+        <v>74675</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2904,25 +2915,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2932,13 +2943,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394746</v>
+        <v>394786</v>
       </c>
       <c r="R20" t="n">
-        <v>7062338</v>
+        <v>7061968</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2991,28 +3002,28 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122481479</v>
+        <v>122483521</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>94859</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3021,25 +3032,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2668</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3049,13 +3060,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394730</v>
+        <v>394553</v>
       </c>
       <c r="R21" t="n">
-        <v>7062309</v>
+        <v>7061889</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3096,40 +3107,30 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122481464</v>
+        <v>122481467</v>
       </c>
       <c r="B22" t="n">
-        <v>78850</v>
+        <v>77699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3142,21 +3143,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3166,10 +3167,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394733</v>
+        <v>394746</v>
       </c>
       <c r="R22" t="n">
-        <v>7062344</v>
+        <v>7062338</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3225,7 +3226,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3243,10 +3244,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122481474</v>
+        <v>122483511</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>78850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3259,45 +3260,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394742</v>
+        <v>394793</v>
       </c>
       <c r="R23" t="n">
-        <v>7062294</v>
+        <v>7062355</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3337,26 +3330,41 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122483523</v>
+        <v>122481486</v>
       </c>
       <c r="B24" t="n">
-        <v>74858</v>
+        <v>79848</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3369,21 +3377,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3393,13 +3401,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394544</v>
+        <v>394648</v>
       </c>
       <c r="R24" t="n">
-        <v>7061898</v>
+        <v>7062211</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3437,7 +3445,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3453,28 +3460,28 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122481486</v>
+        <v>122483532</v>
       </c>
       <c r="B25" t="n">
-        <v>79848</v>
+        <v>82553</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3487,21 +3494,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,13 +3518,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394648</v>
+        <v>394743</v>
       </c>
       <c r="R25" t="n">
-        <v>7062211</v>
+        <v>7062322</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3570,28 +3577,28 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481475</v>
+        <v>122481477</v>
       </c>
       <c r="B26" t="n">
-        <v>79022</v>
+        <v>78929</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3600,25 +3607,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6459</v>
+        <v>1249</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3628,10 +3635,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394738</v>
+        <v>394730</v>
       </c>
       <c r="R26" t="n">
-        <v>7062311</v>
+        <v>7062309</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3687,7 +3694,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3705,10 +3712,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122483514</v>
+        <v>122483537</v>
       </c>
       <c r="B27" t="n">
-        <v>74868</v>
+        <v>78850</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3721,21 +3728,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1467</v>
+        <v>283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3745,10 +3752,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394834</v>
+        <v>394745</v>
       </c>
       <c r="R27" t="n">
-        <v>7062076</v>
+        <v>7062367</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3822,10 +3829,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122481494</v>
+        <v>122483519</v>
       </c>
       <c r="B28" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3838,21 +3845,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3862,13 +3869,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394802</v>
+        <v>394595</v>
       </c>
       <c r="R28" t="n">
-        <v>7062015</v>
+        <v>7061889</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3921,28 +3928,28 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122481495</v>
+        <v>122481494</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3955,21 +3962,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3979,10 +3986,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394826</v>
+        <v>394802</v>
       </c>
       <c r="R29" t="n">
-        <v>7062076</v>
+        <v>7062015</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4038,7 +4045,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4056,10 +4063,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483537</v>
+        <v>122481475</v>
       </c>
       <c r="B30" t="n">
-        <v>78850</v>
+        <v>79022</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4068,25 +4075,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>283</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4096,13 +4103,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394745</v>
+        <v>394738</v>
       </c>
       <c r="R30" t="n">
-        <v>7062367</v>
+        <v>7062311</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4161,22 +4168,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481493</v>
+        <v>122483514</v>
       </c>
       <c r="B31" t="n">
-        <v>78850</v>
+        <v>74868</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4189,21 +4196,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>283</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4213,13 +4220,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394812</v>
+        <v>394834</v>
       </c>
       <c r="R31" t="n">
-        <v>7062006</v>
+        <v>7062076</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4272,25 +4279,25 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122483536</v>
+        <v>122483533</v>
       </c>
       <c r="B32" t="n">
         <v>78929</v>
@@ -4330,10 +4337,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394745</v>
+        <v>394737</v>
       </c>
       <c r="R32" t="n">
-        <v>7062367</v>
+        <v>7062329</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4379,17 +4386,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4524,10 +4531,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122483518</v>
+        <v>122481492</v>
       </c>
       <c r="B34" t="n">
-        <v>78929</v>
+        <v>79883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4536,25 +4543,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1249</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4564,13 +4571,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394636</v>
+        <v>394589</v>
       </c>
       <c r="R34" t="n">
-        <v>7061901</v>
+        <v>7061895</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4613,38 +4620,38 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122483511</v>
+        <v>122481474</v>
       </c>
       <c r="B35" t="n">
-        <v>78850</v>
+        <v>57631</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4657,37 +4664,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>283</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394793</v>
+        <v>394742</v>
       </c>
       <c r="R35" t="n">
-        <v>7062355</v>
+        <v>7062294</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4727,41 +4742,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122481477</v>
+        <v>122483523</v>
       </c>
       <c r="B36" t="n">
-        <v>78929</v>
+        <v>74858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4770,25 +4770,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1249</v>
+        <v>310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394730</v>
+        <v>394544</v>
       </c>
       <c r="R36" t="n">
-        <v>7062309</v>
+        <v>7061898</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4842,6 +4842,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4857,25 +4858,25 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122481482</v>
+        <v>122483535</v>
       </c>
       <c r="B37" t="n">
         <v>78850</v>
@@ -4915,13 +4916,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394669</v>
+        <v>394742</v>
       </c>
       <c r="R37" t="n">
-        <v>7062253</v>
+        <v>7062337</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4974,28 +4975,28 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483535</v>
+        <v>122483536</v>
       </c>
       <c r="B38" t="n">
-        <v>78850</v>
+        <v>78929</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5004,25 +5005,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5032,10 +5033,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394742</v>
+        <v>394745</v>
       </c>
       <c r="R38" t="n">
-        <v>7062337</v>
+        <v>7062367</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -5081,17 +5082,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5109,7 +5110,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481473</v>
+        <v>122481493</v>
       </c>
       <c r="B39" t="n">
         <v>78850</v>
@@ -5149,10 +5150,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394712</v>
+        <v>394812</v>
       </c>
       <c r="R39" t="n">
-        <v>7062279</v>
+        <v>7062006</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5226,10 +5227,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122483534</v>
+        <v>122481495</v>
       </c>
       <c r="B40" t="n">
-        <v>77698</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5238,25 +5239,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6000248</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5266,13 +5267,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394734</v>
+        <v>394826</v>
       </c>
       <c r="R40" t="n">
-        <v>7062334</v>
+        <v>7062076</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5310,7 +5311,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5332,22 +5332,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122481491</v>
+        <v>122483534</v>
       </c>
       <c r="B41" t="n">
-        <v>90962</v>
+        <v>77698</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5356,25 +5356,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6000248</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5384,13 +5384,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394563</v>
+        <v>394734</v>
       </c>
       <c r="R41" t="n">
-        <v>7061882</v>
+        <v>7062334</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5428,6 +5428,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5449,22 +5450,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122483533</v>
+        <v>122481483</v>
       </c>
       <c r="B42" t="n">
-        <v>78929</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5473,41 +5474,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394737</v>
+        <v>394537</v>
       </c>
       <c r="R42" t="n">
-        <v>7062329</v>
+        <v>7061922</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5539,6 +5545,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5547,41 +5558,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122483516</v>
+        <v>122481496</v>
       </c>
       <c r="B43" t="n">
-        <v>79883</v>
+        <v>78929</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5590,25 +5586,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5618,13 +5614,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394830</v>
+        <v>394790</v>
       </c>
       <c r="R43" t="n">
-        <v>7062019</v>
+        <v>7062334</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5662,44 +5658,43 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122483519</v>
+        <v>122481482</v>
       </c>
       <c r="B44" t="n">
-        <v>74863</v>
+        <v>78850</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5712,21 +5707,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5736,13 +5731,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394595</v>
+        <v>394669</v>
       </c>
       <c r="R44" t="n">
-        <v>7061889</v>
+        <v>7062253</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5795,28 +5790,28 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122481483</v>
+        <v>122481473</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78850</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5829,39 +5824,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394537</v>
+        <v>394712</v>
       </c>
       <c r="R45" t="n">
-        <v>7061922</v>
+        <v>7062279</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5896,11 +5886,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5909,6 +5894,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122481467</v>
+        <v>122481466</v>
       </c>
       <c r="B46" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5941,21 +5941,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6042,10 +6042,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122483517</v>
+        <v>122481491</v>
       </c>
       <c r="B47" t="n">
-        <v>74675</v>
+        <v>90962</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6054,25 +6054,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6428</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394786</v>
+        <v>394563</v>
       </c>
       <c r="R47" t="n">
-        <v>7061968</v>
+        <v>7061882</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6147,22 +6147,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122481492</v>
+        <v>122481479</v>
       </c>
       <c r="B48" t="n">
-        <v>79883</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6171,25 +6171,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394589</v>
+        <v>394730</v>
       </c>
       <c r="R48" t="n">
-        <v>7061895</v>
+        <v>7062309</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6248,17 +6248,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122483516</v>
+        <v>122483535</v>
       </c>
       <c r="B17" t="n">
-        <v>79883</v>
+        <v>78850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394830</v>
+        <v>394742</v>
       </c>
       <c r="R17" t="n">
-        <v>7062019</v>
+        <v>7062337</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2635,23 +2635,22 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2669,7 +2668,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122483518</v>
+        <v>122483533</v>
       </c>
       <c r="B18" t="n">
         <v>78929</v>
@@ -2709,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394636</v>
+        <v>394737</v>
       </c>
       <c r="R18" t="n">
-        <v>7061901</v>
+        <v>7062329</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2786,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122481464</v>
+        <v>122483521</v>
       </c>
       <c r="B19" t="n">
-        <v>78850</v>
+        <v>94861</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2798,25 +2797,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>2668</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2826,13 +2825,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394733</v>
+        <v>394553</v>
       </c>
       <c r="R19" t="n">
-        <v>7062344</v>
+        <v>7061889</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2873,40 +2872,30 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122483517</v>
+        <v>122483514</v>
       </c>
       <c r="B20" t="n">
-        <v>74675</v>
+        <v>74868</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2915,25 +2904,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6428</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2943,10 +2932,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394786</v>
+        <v>394834</v>
       </c>
       <c r="R20" t="n">
-        <v>7061968</v>
+        <v>7062076</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -3020,10 +3009,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122483521</v>
+        <v>122481475</v>
       </c>
       <c r="B21" t="n">
-        <v>94859</v>
+        <v>79022</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3036,21 +3025,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2668</v>
+        <v>6459</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3060,13 +3049,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394553</v>
+        <v>394738</v>
       </c>
       <c r="R21" t="n">
-        <v>7061889</v>
+        <v>7062311</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3107,20 +3096,30 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3244,10 +3243,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122483511</v>
+        <v>122483534</v>
       </c>
       <c r="B23" t="n">
-        <v>78850</v>
+        <v>77698</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3256,25 +3255,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>6000248</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3284,10 +3283,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394793</v>
+        <v>394734</v>
       </c>
       <c r="R23" t="n">
-        <v>7062355</v>
+        <v>7062334</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3328,6 +3327,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122481486</v>
+        <v>122481466</v>
       </c>
       <c r="B24" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3377,21 +3377,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394648</v>
+        <v>394746</v>
       </c>
       <c r="R24" t="n">
-        <v>7062211</v>
+        <v>7062338</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>grankvistar # Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122483532</v>
+        <v>122483516</v>
       </c>
       <c r="B25" t="n">
-        <v>82553</v>
+        <v>79883</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3490,25 +3490,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394743</v>
+        <v>394830</v>
       </c>
       <c r="R25" t="n">
-        <v>7062322</v>
+        <v>7062019</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3562,22 +3562,23 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3595,10 +3596,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481477</v>
+        <v>122481495</v>
       </c>
       <c r="B26" t="n">
-        <v>78929</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3607,25 +3608,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3635,10 +3636,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394730</v>
+        <v>394826</v>
       </c>
       <c r="R26" t="n">
-        <v>7062309</v>
+        <v>7062076</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3694,7 +3695,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3712,10 +3713,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122483537</v>
+        <v>122483523</v>
       </c>
       <c r="B27" t="n">
-        <v>78850</v>
+        <v>74858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3728,21 +3729,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3752,10 +3753,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394745</v>
+        <v>394544</v>
       </c>
       <c r="R27" t="n">
-        <v>7062367</v>
+        <v>7061898</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3796,6 +3797,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3829,10 +3831,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122483519</v>
+        <v>122483537</v>
       </c>
       <c r="B28" t="n">
-        <v>74863</v>
+        <v>78850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3845,21 +3847,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3869,10 +3871,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394595</v>
+        <v>394745</v>
       </c>
       <c r="R28" t="n">
-        <v>7061889</v>
+        <v>7062367</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3946,10 +3948,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122481494</v>
+        <v>122483511</v>
       </c>
       <c r="B29" t="n">
-        <v>77699</v>
+        <v>78850</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3962,21 +3964,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3986,13 +3988,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394802</v>
+        <v>394793</v>
       </c>
       <c r="R29" t="n">
-        <v>7062015</v>
+        <v>7062355</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4045,28 +4047,28 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122481475</v>
+        <v>122483529</v>
       </c>
       <c r="B30" t="n">
-        <v>79022</v>
+        <v>78929</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4075,25 +4077,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>1249</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4103,13 +4105,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394738</v>
+        <v>394652</v>
       </c>
       <c r="R30" t="n">
-        <v>7062311</v>
+        <v>7062221</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4168,22 +4170,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122483514</v>
+        <v>122481492</v>
       </c>
       <c r="B31" t="n">
-        <v>74868</v>
+        <v>79883</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4192,25 +4194,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4220,13 +4222,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394834</v>
+        <v>394589</v>
       </c>
       <c r="R31" t="n">
-        <v>7062076</v>
+        <v>7061895</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4269,35 +4271,35 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122483533</v>
+        <v>122483518</v>
       </c>
       <c r="B32" t="n">
         <v>78929</v>
@@ -4337,10 +4339,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394737</v>
+        <v>394636</v>
       </c>
       <c r="R32" t="n">
-        <v>7062329</v>
+        <v>7061901</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4414,7 +4416,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483529</v>
+        <v>122483536</v>
       </c>
       <c r="B33" t="n">
         <v>78929</v>
@@ -4454,10 +4456,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394652</v>
+        <v>394745</v>
       </c>
       <c r="R33" t="n">
-        <v>7062221</v>
+        <v>7062367</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4503,17 +4505,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4531,10 +4533,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481492</v>
+        <v>122481477</v>
       </c>
       <c r="B34" t="n">
-        <v>79883</v>
+        <v>78929</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4543,25 +4545,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4571,10 +4573,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394589</v>
+        <v>394730</v>
       </c>
       <c r="R34" t="n">
-        <v>7061895</v>
+        <v>7062309</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4620,17 +4622,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4648,10 +4650,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122481474</v>
+        <v>122481496</v>
       </c>
       <c r="B35" t="n">
-        <v>57631</v>
+        <v>78929</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4660,46 +4662,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>1249</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394742</v>
+        <v>394790</v>
       </c>
       <c r="R35" t="n">
-        <v>7062294</v>
+        <v>7062334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4742,6 +4736,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>på granar gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4758,10 +4767,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122483523</v>
+        <v>122481482</v>
       </c>
       <c r="B36" t="n">
-        <v>74858</v>
+        <v>78850</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4774,21 +4783,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4798,13 +4807,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394544</v>
+        <v>394669</v>
       </c>
       <c r="R36" t="n">
-        <v>7061898</v>
+        <v>7062253</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4842,7 +4851,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4858,28 +4866,28 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483535</v>
+        <v>122483519</v>
       </c>
       <c r="B37" t="n">
-        <v>78850</v>
+        <v>74863</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4892,21 +4900,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4916,10 +4924,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394742</v>
+        <v>394595</v>
       </c>
       <c r="R37" t="n">
-        <v>7062337</v>
+        <v>7061889</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4993,10 +5001,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483536</v>
+        <v>122481483</v>
       </c>
       <c r="B38" t="n">
-        <v>78929</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5005,41 +5013,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394745</v>
+        <v>394537</v>
       </c>
       <c r="R38" t="n">
-        <v>7062367</v>
+        <v>7061922</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5071,6 +5084,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5079,41 +5097,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122481493</v>
+        <v>122483532</v>
       </c>
       <c r="B39" t="n">
-        <v>78850</v>
+        <v>82553</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5126,21 +5129,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>283</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5150,13 +5153,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394812</v>
+        <v>394743</v>
       </c>
       <c r="R39" t="n">
-        <v>7062006</v>
+        <v>7062322</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5209,28 +5212,28 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122481495</v>
+        <v>122481464</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>78850</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5243,21 +5246,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5267,10 +5270,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394826</v>
+        <v>394733</v>
       </c>
       <c r="R40" t="n">
-        <v>7062076</v>
+        <v>7062344</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5326,7 +5329,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5344,10 +5347,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122483534</v>
+        <v>122481473</v>
       </c>
       <c r="B41" t="n">
-        <v>77698</v>
+        <v>78850</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5356,25 +5359,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6000248</v>
+        <v>283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5384,13 +5387,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394734</v>
+        <v>394712</v>
       </c>
       <c r="R41" t="n">
-        <v>7062334</v>
+        <v>7062279</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5428,7 +5431,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5444,28 +5446,28 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481483</v>
+        <v>122481491</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5478,39 +5480,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394537</v>
+        <v>394563</v>
       </c>
       <c r="R42" t="n">
-        <v>7061922</v>
+        <v>7061882</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5545,11 +5542,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5558,6 +5550,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5574,10 +5581,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481496</v>
+        <v>122481494</v>
       </c>
       <c r="B43" t="n">
-        <v>78929</v>
+        <v>77699</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5586,25 +5593,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5614,10 +5621,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394790</v>
+        <v>394802</v>
       </c>
       <c r="R43" t="n">
-        <v>7062334</v>
+        <v>7062015</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5673,7 +5680,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5691,7 +5698,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481482</v>
+        <v>122481493</v>
       </c>
       <c r="B44" t="n">
         <v>78850</v>
@@ -5731,10 +5738,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394669</v>
+        <v>394812</v>
       </c>
       <c r="R44" t="n">
-        <v>7062253</v>
+        <v>7062006</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5808,10 +5815,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122481473</v>
+        <v>122481486</v>
       </c>
       <c r="B45" t="n">
-        <v>78850</v>
+        <v>79848</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5824,21 +5831,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>283</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5848,10 +5855,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394712</v>
+        <v>394648</v>
       </c>
       <c r="R45" t="n">
-        <v>7062279</v>
+        <v>7062211</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5907,7 +5914,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5925,10 +5932,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122481466</v>
+        <v>122481479</v>
       </c>
       <c r="B46" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5941,21 +5948,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5965,10 +5972,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394746</v>
+        <v>394730</v>
       </c>
       <c r="R46" t="n">
-        <v>7062338</v>
+        <v>7062309</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6024,7 +6031,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6042,10 +6049,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122481491</v>
+        <v>122483517</v>
       </c>
       <c r="B47" t="n">
-        <v>90962</v>
+        <v>74675</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6054,25 +6061,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6428</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6082,13 +6089,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394563</v>
+        <v>394786</v>
       </c>
       <c r="R47" t="n">
-        <v>7061882</v>
+        <v>7061968</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6147,22 +6154,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122481479</v>
+        <v>122481474</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6175,34 +6182,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394730</v>
+        <v>394742</v>
       </c>
       <c r="R48" t="n">
-        <v>7062309</v>
+        <v>7062294</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6245,21 +6260,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -3126,10 +3126,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122481467</v>
+        <v>122481466</v>
       </c>
       <c r="B22" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122481466</v>
+        <v>122481467</v>
       </c>
       <c r="B24" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3377,21 +3377,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122483516</v>
+        <v>122483523</v>
       </c>
       <c r="B25" t="n">
-        <v>79883</v>
+        <v>74858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3490,25 +3490,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394830</v>
+        <v>394544</v>
       </c>
       <c r="R25" t="n">
-        <v>7062019</v>
+        <v>7061898</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3568,17 +3568,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122481495</v>
+        <v>122483537</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>78850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394826</v>
+        <v>394745</v>
       </c>
       <c r="R26" t="n">
-        <v>7062076</v>
+        <v>7062367</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3701,22 +3701,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122483523</v>
+        <v>122483511</v>
       </c>
       <c r="B27" t="n">
-        <v>74858</v>
+        <v>78850</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3729,21 +3729,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394544</v>
+        <v>394793</v>
       </c>
       <c r="R27" t="n">
-        <v>7061898</v>
+        <v>7062355</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3797,7 +3797,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3831,10 +3830,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122483537</v>
+        <v>122483516</v>
       </c>
       <c r="B28" t="n">
-        <v>78850</v>
+        <v>79883</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3843,25 +3842,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3871,10 +3870,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394745</v>
+        <v>394830</v>
       </c>
       <c r="R28" t="n">
-        <v>7062367</v>
+        <v>7062019</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3915,22 +3914,23 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122483511</v>
+        <v>122481495</v>
       </c>
       <c r="B29" t="n">
-        <v>78850</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3988,13 +3988,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394793</v>
+        <v>394826</v>
       </c>
       <c r="R29" t="n">
-        <v>7062355</v>
+        <v>7062076</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4053,12 +4053,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4533,7 +4533,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481477</v>
+        <v>122481496</v>
       </c>
       <c r="B34" t="n">
         <v>78929</v>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394730</v>
+        <v>394790</v>
       </c>
       <c r="R34" t="n">
-        <v>7062309</v>
+        <v>7062334</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>på granar gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4650,7 +4650,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122481496</v>
+        <v>122481477</v>
       </c>
       <c r="B35" t="n">
         <v>78929</v>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394790</v>
+        <v>394730</v>
       </c>
       <c r="R35" t="n">
-        <v>7062334</v>
+        <v>7062309</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>grenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>359713</v>
+        <v>122481464</v>
       </c>
       <c r="B2" t="n">
-        <v>77667</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394557.8778961392</v>
+        <v>394733</v>
       </c>
       <c r="R2" t="n">
-        <v>7062134.564145572</v>
+        <v>7062344</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,44 +757,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>354971</v>
+        <v>122481473</v>
       </c>
       <c r="B3" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394597.6209695217</v>
+        <v>394712</v>
       </c>
       <c r="R3" t="n">
-        <v>7062059.046710067</v>
+        <v>7062279</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,82 +869,78 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>864595</v>
+        <v>122481482</v>
       </c>
       <c r="B4" t="n">
-        <v>93043</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394625.0733313222</v>
+        <v>394669</v>
       </c>
       <c r="R4" t="n">
-        <v>7062255.381335978</v>
+        <v>7062253</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,82 +981,78 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2927187</v>
+        <v>122481488</v>
       </c>
       <c r="B5" t="n">
-        <v>95716</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220686</v>
+        <v>283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394586.2111338919</v>
+        <v>394529</v>
       </c>
       <c r="R5" t="n">
-        <v>7062183.820288323</v>
+        <v>7061895</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,44 +1093,40 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1553796</v>
+        <v>122481493</v>
       </c>
       <c r="B6" t="n">
-        <v>89409</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,37 +1134,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394635.3215814176</v>
+        <v>394812</v>
       </c>
       <c r="R6" t="n">
-        <v>7061988.927540644</v>
+        <v>7062006</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1188,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,82 +1205,78 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>kvistar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>359714</v>
+        <v>122483511</v>
       </c>
       <c r="B7" t="n">
-        <v>77667</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394575.4166281857</v>
+        <v>394793</v>
       </c>
       <c r="R7" t="n">
-        <v>7062086.887380789</v>
+        <v>7062355</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1375,22 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,82 +1317,78 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2062925</v>
+        <v>122483535</v>
       </c>
       <c r="B8" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394288.2903914378</v>
+        <v>394742</v>
       </c>
       <c r="R8" t="n">
-        <v>7061921.428111137</v>
+        <v>7062337</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1501,22 +1412,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,82 +1429,78 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>359711</v>
+        <v>122483537</v>
       </c>
       <c r="B9" t="n">
-        <v>77667</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394623.6090504969</v>
+        <v>394745</v>
       </c>
       <c r="R9" t="n">
-        <v>7062211.449851954</v>
+        <v>7062367</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,22 +1524,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,44 +1541,40 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>354970</v>
+        <v>122483523</v>
       </c>
       <c r="B10" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,37 +1582,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394578.2872969713</v>
+        <v>394544</v>
       </c>
       <c r="R10" t="n">
-        <v>7062172.978160464</v>
+        <v>7061898</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1753,22 +1636,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1777,47 +1650,44 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>359712</v>
+        <v>359711</v>
       </c>
       <c r="B11" t="n">
-        <v>77667</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394601.1408977459</v>
+        <v>394624</v>
       </c>
       <c r="R11" t="n">
-        <v>7062191.319065875</v>
+        <v>7062211</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1882,19 +1752,9 @@
           <t>2010-06-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,37 +1795,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4387161</v>
+        <v>359712</v>
       </c>
       <c r="B12" t="n">
-        <v>96353</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>1249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1975,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394636.4762263337</v>
+        <v>394601</v>
       </c>
       <c r="R12" t="n">
-        <v>7062290.540463923</v>
+        <v>7062191</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2008,19 +1863,9 @@
           <t>2010-06-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,37 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1677897</v>
+        <v>359713</v>
       </c>
       <c r="B13" t="n">
-        <v>89355</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2101,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394578.2872969713</v>
+        <v>394558</v>
       </c>
       <c r="R13" t="n">
-        <v>7062172.978160464</v>
+        <v>7062135</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2134,19 +1974,9 @@
           <t>2010-06-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2187,37 +2017,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1839793</v>
+        <v>359714</v>
       </c>
       <c r="B14" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2227,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394601.1408977459</v>
+        <v>394575</v>
       </c>
       <c r="R14" t="n">
-        <v>7062191.319065875</v>
+        <v>7062087</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2260,19 +2085,9 @@
           <t>2010-06-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2313,53 +2128,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>59731260</v>
+        <v>122481477</v>
       </c>
       <c r="B15" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220686</v>
+        <v>1249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Segerdalen, ca 1 km öster om Sundet, ca 500 m väster om Fallet,, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394727.4560922029</v>
+        <v>394730</v>
       </c>
       <c r="R15" t="n">
-        <v>7061976.972973824</v>
+        <v>7062309</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2383,27 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gammal granskog</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2414,69 +2209,79 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>grenar på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>62065515</v>
+        <v>122481496</v>
       </c>
       <c r="B16" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>1249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sundet / V /, Jmt</t>
+          <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394727.4560922029</v>
+        <v>394790</v>
       </c>
       <c r="R16" t="n">
-        <v>7061976.972973824</v>
+        <v>7062334</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2500,27 +2305,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1997-10-11</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1997-10-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Öster om bäcken på båda sidor om vägen till Fallet. Segerdalen, ca 1 km öster om Sundet, ca 500 m väster om Fallet,</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2531,57 +2321,63 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>på granar gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122483535</v>
+        <v>122483518</v>
       </c>
       <c r="B17" t="n">
-        <v>78850</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2591,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394742</v>
+        <v>394636</v>
       </c>
       <c r="R17" t="n">
-        <v>7062337</v>
+        <v>7061901</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2668,15 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122483533</v>
+        <v>122483529</v>
       </c>
       <c r="B18" t="n">
-        <v>78929</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394737</v>
+        <v>394652</v>
       </c>
       <c r="R18" t="n">
-        <v>7062329</v>
+        <v>7062221</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2785,37 +2576,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122483521</v>
+        <v>122483533</v>
       </c>
       <c r="B19" t="n">
-        <v>94861</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2668</v>
+        <v>1249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2825,10 +2611,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394553</v>
+        <v>394737</v>
       </c>
       <c r="R19" t="n">
-        <v>7061889</v>
+        <v>7062329</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2872,9 +2658,19 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Lodyta, intermediär</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2892,37 +2688,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122483514</v>
+        <v>122483536</v>
       </c>
       <c r="B20" t="n">
-        <v>74868</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2932,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394834</v>
+        <v>394745</v>
       </c>
       <c r="R20" t="n">
-        <v>7062076</v>
+        <v>7062367</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2981,17 +2772,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3009,53 +2800,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122481475</v>
+        <v>354970</v>
       </c>
       <c r="B21" t="n">
-        <v>79022</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6459</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Sundet O, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394738</v>
+        <v>394578</v>
       </c>
       <c r="R21" t="n">
-        <v>7062311</v>
+        <v>7062173</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3079,12 +2865,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3096,45 +2882,39 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122481466</v>
+        <v>354971</v>
       </c>
       <c r="B22" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3142,37 +2922,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Sundet O, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394746</v>
+        <v>394598</v>
       </c>
       <c r="R22" t="n">
-        <v>7062338</v>
+        <v>7062059</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3196,12 +2976,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3213,67 +2993,61 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>bark på gammal gran # Picea abies</t>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122483534</v>
+        <v>122483532</v>
       </c>
       <c r="B23" t="n">
-        <v>77698</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6000248</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3283,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394734</v>
+        <v>394743</v>
       </c>
       <c r="R23" t="n">
-        <v>7062334</v>
+        <v>7062322</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3327,7 +3101,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3361,15 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122481467</v>
+        <v>122483514</v>
       </c>
       <c r="B24" t="n">
-        <v>77699</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,21 +3145,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3401,13 +3169,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394746</v>
+        <v>394834</v>
       </c>
       <c r="R24" t="n">
-        <v>7062338</v>
+        <v>7062076</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3460,33 +3228,28 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>bark på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122483523</v>
+        <v>122481486</v>
       </c>
       <c r="B25" t="n">
-        <v>74858</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3494,21 +3257,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3518,13 +3281,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394544</v>
+        <v>394648</v>
       </c>
       <c r="R25" t="n">
-        <v>7061898</v>
+        <v>7062211</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3562,7 +3325,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3578,55 +3340,50 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grankvistar # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122483537</v>
+        <v>122483521</v>
       </c>
       <c r="B26" t="n">
-        <v>78850</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>283</v>
+        <v>2668</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3636,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394745</v>
+        <v>394553</v>
       </c>
       <c r="R26" t="n">
-        <v>7062367</v>
+        <v>7061889</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3683,19 +3440,9 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lodyta, intermediär</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3713,53 +3460,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122483511</v>
+        <v>864595</v>
       </c>
       <c r="B27" t="n">
-        <v>78850</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>283</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Sundet O, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394793</v>
+        <v>394625</v>
       </c>
       <c r="R27" t="n">
-        <v>7062355</v>
+        <v>7062255</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3783,12 +3525,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3800,45 +3542,39 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122483516</v>
+        <v>122483528</v>
       </c>
       <c r="B28" t="n">
-        <v>79883</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,21 +3582,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3870,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394830</v>
+        <v>394510</v>
       </c>
       <c r="R28" t="n">
-        <v>7062019</v>
+        <v>7061897</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3914,24 +3650,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3948,37 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122481495</v>
+        <v>122481490</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3988,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394826</v>
+        <v>394490</v>
       </c>
       <c r="R29" t="n">
-        <v>7062076</v>
+        <v>7061925</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4065,53 +3780,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122483529</v>
+        <v>1677897</v>
       </c>
       <c r="B30" t="n">
-        <v>78929</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1249</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Sundet O, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394652</v>
+        <v>394578</v>
       </c>
       <c r="R30" t="n">
-        <v>7062221</v>
+        <v>7062173</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4135,12 +3845,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4152,83 +3862,77 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122481492</v>
+        <v>1839793</v>
       </c>
       <c r="B31" t="n">
-        <v>79883</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Sundet O, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394589</v>
+        <v>394601</v>
       </c>
       <c r="R31" t="n">
-        <v>7061895</v>
+        <v>7062191</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4252,12 +3956,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4269,45 +3973,39 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122483518</v>
+        <v>122481479</v>
       </c>
       <c r="B32" t="n">
-        <v>78929</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4315,21 +4013,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4339,13 +4037,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394636</v>
+        <v>394730</v>
       </c>
       <c r="R32" t="n">
-        <v>7061901</v>
+        <v>7062309</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4404,27 +4102,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122483536</v>
+        <v>122481495</v>
       </c>
       <c r="B33" t="n">
-        <v>78929</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4432,21 +4125,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4456,13 +4149,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394745</v>
+        <v>394826</v>
       </c>
       <c r="R33" t="n">
-        <v>7062367</v>
+        <v>7062076</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4505,65 +4198,60 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122481496</v>
+        <v>122481489</v>
       </c>
       <c r="B34" t="n">
-        <v>78929</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1249</v>
+        <v>6428</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4573,10 +4261,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394790</v>
+        <v>394510</v>
       </c>
       <c r="R34" t="n">
-        <v>7062334</v>
+        <v>7061906</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4632,7 +4320,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>på granar gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4650,37 +4338,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122481477</v>
+        <v>122483517</v>
       </c>
       <c r="B35" t="n">
-        <v>78929</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1249</v>
+        <v>6428</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4690,13 +4373,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394730</v>
+        <v>394786</v>
       </c>
       <c r="R35" t="n">
-        <v>7062309</v>
+        <v>7061968</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4749,55 +4432,50 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>grenar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122481482</v>
+        <v>122483526</v>
       </c>
       <c r="B36" t="n">
-        <v>78850</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>283</v>
+        <v>6428</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4807,13 +4485,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394669</v>
+        <v>394516</v>
       </c>
       <c r="R36" t="n">
-        <v>7062253</v>
+        <v>7061906</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4866,33 +4544,28 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483519</v>
+        <v>122481466</v>
       </c>
       <c r="B37" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4924,13 +4597,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394595</v>
+        <v>394746</v>
       </c>
       <c r="R37" t="n">
-        <v>7061889</v>
+        <v>7062338</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4983,33 +4656,28 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>bark på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122481483</v>
+        <v>122483519</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5017,42 +4685,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394537</v>
+        <v>394595</v>
       </c>
       <c r="R38" t="n">
-        <v>7061922</v>
+        <v>7061889</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5084,11 +4747,6 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>färska spår, hack i "schackrutemönster"</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5097,53 +4755,63 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122483532</v>
+        <v>122481475</v>
       </c>
       <c r="B39" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5153,13 +4821,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394743</v>
+        <v>394738</v>
       </c>
       <c r="R39" t="n">
-        <v>7062322</v>
+        <v>7062311</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5218,49 +4886,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122481464</v>
+        <v>122483513</v>
       </c>
       <c r="B40" t="n">
-        <v>78850</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>283</v>
+        <v>6459</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5270,13 +4933,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394733</v>
+        <v>394868</v>
       </c>
       <c r="R40" t="n">
-        <v>7062344</v>
+        <v>7062117</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5314,86 +4977,82 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122481473</v>
+        <v>2062925</v>
       </c>
       <c r="B41" t="n">
-        <v>78850</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>283</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Sundet O, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394712</v>
+        <v>394288</v>
       </c>
       <c r="R41" t="n">
-        <v>7062279</v>
+        <v>7061921</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5417,12 +5076,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2010-06-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5434,67 +5093,61 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>kvistar på gammal gran # Picea abies</t>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122481491</v>
+        <v>122481492</v>
       </c>
       <c r="B42" t="n">
-        <v>90962</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5504,10 +5157,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394563</v>
+        <v>394589</v>
       </c>
       <c r="R42" t="n">
-        <v>7061882</v>
+        <v>7061895</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5553,17 +5206,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5581,37 +5234,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122481494</v>
+        <v>122483516</v>
       </c>
       <c r="B43" t="n">
-        <v>77699</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5621,13 +5269,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394802</v>
+        <v>394830</v>
       </c>
       <c r="R43" t="n">
-        <v>7062015</v>
+        <v>7062019</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5665,48 +5313,44 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122481493</v>
+        <v>122481483</v>
       </c>
       <c r="B44" t="n">
-        <v>78850</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5714,34 +5358,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394812</v>
+        <v>394537</v>
       </c>
       <c r="R44" t="n">
-        <v>7062006</v>
+        <v>7061922</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5776,6 +5425,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5784,21 +5438,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>kvistar på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5815,15 +5454,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122481486</v>
+        <v>122481485</v>
       </c>
       <c r="B45" t="n">
-        <v>79848</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5831,34 +5465,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394648</v>
+        <v>394503</v>
       </c>
       <c r="R45" t="n">
-        <v>7062211</v>
+        <v>7062083</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5893,6 +5532,11 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>färska spår, hack i "schackrutemönster"</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5901,21 +5545,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>grankvistar # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5932,50 +5561,51 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122481479</v>
+        <v>14984223</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>101248</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Kall, Sydost om Sundet, vägen till Fallet,, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394730</v>
+        <v>394248</v>
       </c>
       <c r="R46" t="n">
-        <v>7062309</v>
+        <v>7061926</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6002,100 +5632,102 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2008-06-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2008-06-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 ex. skäligen misstänkt violett guldvinge. Blåste bort för snabbt för säker artbestämning. Bör sökas vid bättre väderförhållanden. Solglimtar, ca 15 grader, vindbyar. Solexponerat läge mot skogsbryn, vid stort båthus.</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Mindre väg med vegetationsbevuxen mittremsa med bl.a. ormrot,</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122483517</v>
+        <v>122481474</v>
       </c>
       <c r="B47" t="n">
-        <v>74675</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6428</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394786</v>
+        <v>394742</v>
       </c>
       <c r="R47" t="n">
-        <v>7061968</v>
+        <v>7062294</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6135,46 +5767,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122481474</v>
+        <v>122481484</v>
       </c>
       <c r="B48" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6200,24 +5812,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394742</v>
+        <v>394538</v>
       </c>
       <c r="R48" t="n">
-        <v>7062294</v>
+        <v>7062004</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6247,9 +5851,19 @@
           <t>2025-02-05</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6273,6 +5887,565 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2927187</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sundet O, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>394586</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7062184</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2010-06-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2010-06-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4387161</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sundet O, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>394636</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7062291</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2010-06-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2010-06-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122481467</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>394746</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7062338</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>bark på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122481494</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>394802</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7062015</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122483534</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78338</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>394734</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7062334</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481464</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481473</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481482</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481488</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481493</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483511</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483535</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483537</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,6 +1726,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483523</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/359711</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/359712</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2014,6 +2074,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/359713</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2125,6 +2190,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/359714</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2237,6 +2307,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481477</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2349,6 +2424,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481496</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2461,6 +2541,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483518</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2573,6 +2658,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483529</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2685,6 +2775,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483533</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2797,6 +2892,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483536</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2908,6 +3008,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/354970</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3019,6 +3124,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/354971</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3131,6 +3241,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483532</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3243,6 +3358,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483514</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3355,6 +3475,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481486</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3457,6 +3582,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483521</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3568,6 +3698,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/864595</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3665,6 +3800,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483528</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3777,6 +3917,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481490</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3888,6 +4033,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1677897</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3999,6 +4149,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1839793</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4111,6 +4266,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481479</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4223,6 +4383,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481495</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4335,6 +4500,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481489</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4447,6 +4617,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483517</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4559,6 +4734,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483526</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4671,6 +4851,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481466</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4783,6 +4968,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483519</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4895,6 +5085,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481475</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5008,6 +5203,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483513</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5119,6 +5319,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2062925</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5231,6 +5436,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481492</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5344,6 +5554,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483516</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5451,6 +5666,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481483</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5558,6 +5778,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481485</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5675,6 +5900,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14984223</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5780,6 +6010,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481474</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5887,6 +6122,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481484</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5998,6 +6238,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2927187</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6109,6 +6354,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4387161</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6221,6 +6471,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481467</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6333,6 +6588,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481494</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6446,8 +6706,67 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122483534</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>